--- a/research/traditional_assets/database/data/kenya/kenya_oilfield_svcs_equip.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_oilfield_svcs_equip.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1604381941031025</v>
+        <v>0.1599883795207932</v>
       </c>
       <c r="C2">
-        <v>103.0552516327772</v>
+        <v>102.1957075135145</v>
       </c>
       <c r="D2">
-        <v>81.95525163277721</v>
+        <v>82.12410751351453</v>
       </c>
       <c r="E2">
-        <v>-5.64</v>
+        <v>-4.611599999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.0284</v>
       </c>
       <c r="G2">
         <v>21.1</v>
@@ -1451,28 +1451,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.05172851999999999</v>
       </c>
       <c r="N2">
-        <v>62.46666666666667</v>
+        <v>62.41493814666667</v>
       </c>
       <c r="O2">
-        <v>18.74</v>
+        <v>18.724481444</v>
       </c>
       <c r="P2">
-        <v>43.72666666666667</v>
+        <v>43.69045670266667</v>
       </c>
       <c r="Q2">
-        <v>59.42666666666668</v>
+        <v>59.39045670266667</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1604381941031025</v>
+        <v>0.1612487671927204</v>
       </c>
       <c r="T2">
-        <v>0.7993082229751833</v>
+        <v>0.8049598972790483</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>1207.586582153649</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1599883795207932</v>
+        <v>0.1595385649384839</v>
       </c>
       <c r="C3">
-        <v>102.1957075135145</v>
+        <v>101.3368606326666</v>
       </c>
       <c r="D3">
-        <v>82.12410751351453</v>
+        <v>82.29366063266656</v>
       </c>
       <c r="E3">
-        <v>-4.611599999999999</v>
+        <v>-3.5832</v>
       </c>
       <c r="F3">
-        <v>1.0284</v>
+        <v>2.0568</v>
       </c>
       <c r="G3">
         <v>21.1</v>
@@ -1533,28 +1533,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M3">
-        <v>0.05172851999999999</v>
+        <v>0.10345704</v>
       </c>
       <c r="N3">
-        <v>62.41493814666667</v>
+        <v>62.36320962666667</v>
       </c>
       <c r="O3">
-        <v>18.724481444</v>
+        <v>18.708962888</v>
       </c>
       <c r="P3">
-        <v>43.69045670266667</v>
+        <v>43.65424673866667</v>
       </c>
       <c r="Q3">
-        <v>59.39045670266667</v>
+        <v>59.35424673866667</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1612487671927204</v>
+        <v>0.1620758825902897</v>
       </c>
       <c r="T3">
-        <v>0.8049598972790483</v>
+        <v>0.8107269118748288</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>1207.586582153649</v>
+        <v>603.7932910768245</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1595385649384839</v>
+        <v>0.1590887503561746</v>
       </c>
       <c r="C4">
-        <v>101.3368606326666</v>
+        <v>100.4787153177151</v>
       </c>
       <c r="D4">
-        <v>82.29366063266656</v>
+        <v>82.46391531771512</v>
       </c>
       <c r="E4">
-        <v>-3.5832</v>
+        <v>-2.5548</v>
       </c>
       <c r="F4">
-        <v>2.0568</v>
+        <v>3.0852</v>
       </c>
       <c r="G4">
         <v>21.1</v>
@@ -1615,28 +1615,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M4">
-        <v>0.10345704</v>
+        <v>0.15518556</v>
       </c>
       <c r="N4">
-        <v>62.36320962666667</v>
+        <v>62.31148110666667</v>
       </c>
       <c r="O4">
-        <v>18.708962888</v>
+        <v>18.693444332</v>
       </c>
       <c r="P4">
-        <v>43.65424673866667</v>
+        <v>43.61803677466667</v>
       </c>
       <c r="Q4">
-        <v>59.35424673866667</v>
+        <v>59.31803677466667</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1620758825902897</v>
+        <v>0.1629200519135821</v>
       </c>
       <c r="T4">
-        <v>0.8107269118748288</v>
+        <v>0.8166128339880481</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>603.7932910768245</v>
+        <v>402.5288607178829</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1590887503561746</v>
+        <v>0.1586389357738653</v>
       </c>
       <c r="C5">
-        <v>100.4787153177151</v>
+        <v>99.62127593202821</v>
       </c>
       <c r="D5">
-        <v>82.46391531771512</v>
+        <v>82.63487593202821</v>
       </c>
       <c r="E5">
-        <v>-2.5548</v>
+        <v>-1.5264</v>
       </c>
       <c r="F5">
-        <v>3.0852</v>
+        <v>4.1136</v>
       </c>
       <c r="G5">
         <v>21.1</v>
@@ -1697,28 +1697,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M5">
-        <v>0.15518556</v>
+        <v>0.20691408</v>
       </c>
       <c r="N5">
-        <v>62.31148110666667</v>
+        <v>62.25975258666667</v>
       </c>
       <c r="O5">
-        <v>18.693444332</v>
+        <v>18.677925776</v>
       </c>
       <c r="P5">
-        <v>43.61803677466667</v>
+        <v>43.58182681066667</v>
       </c>
       <c r="Q5">
-        <v>59.31803677466667</v>
+        <v>59.28182681066667</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1629200519135821</v>
+        <v>0.1637818080977763</v>
       </c>
       <c r="T5">
-        <v>0.8166128339880481</v>
+        <v>0.8226213794786261</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>402.5288607178829</v>
+        <v>301.8966455384123</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1586389357738653</v>
+        <v>0.158189121191556</v>
       </c>
       <c r="C6">
-        <v>99.62127593202821</v>
+        <v>98.76454687523284</v>
       </c>
       <c r="D6">
-        <v>82.63487593202821</v>
+        <v>82.80654687523283</v>
       </c>
       <c r="E6">
-        <v>-1.5264</v>
+        <v>-0.4979999999999993</v>
       </c>
       <c r="F6">
-        <v>4.1136</v>
+        <v>5.142</v>
       </c>
       <c r="G6">
         <v>21.1</v>
@@ -1779,28 +1779,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M6">
-        <v>0.20691408</v>
+        <v>0.2586426</v>
       </c>
       <c r="N6">
-        <v>62.25975258666667</v>
+        <v>62.20802406666667</v>
       </c>
       <c r="O6">
-        <v>18.677925776</v>
+        <v>18.66240722</v>
       </c>
       <c r="P6">
-        <v>43.58182681066667</v>
+        <v>43.54561684666667</v>
       </c>
       <c r="Q6">
-        <v>59.28182681066667</v>
+        <v>59.24561684666666</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1637818080977763</v>
+        <v>0.1646617065174273</v>
       </c>
       <c r="T6">
-        <v>0.8226213794786261</v>
+        <v>0.8287564206637427</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>301.8966455384123</v>
+        <v>241.5173164307298</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.158189121191556</v>
+        <v>0.1577393066092466</v>
       </c>
       <c r="C7">
-        <v>98.76454687523284</v>
+        <v>97.90853258359226</v>
       </c>
       <c r="D7">
-        <v>82.80654687523283</v>
+        <v>82.97893258359225</v>
       </c>
       <c r="E7">
-        <v>-0.4979999999999993</v>
+        <v>0.5304000000000011</v>
       </c>
       <c r="F7">
-        <v>5.142</v>
+        <v>6.170400000000001</v>
       </c>
       <c r="G7">
         <v>21.1</v>
@@ -1861,28 +1861,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M7">
-        <v>0.2586426</v>
+        <v>0.31037112</v>
       </c>
       <c r="N7">
-        <v>62.20802406666667</v>
+        <v>62.15629554666667</v>
       </c>
       <c r="O7">
-        <v>18.66240722</v>
+        <v>18.646888664</v>
       </c>
       <c r="P7">
-        <v>43.54561684666667</v>
+        <v>43.50940688266667</v>
       </c>
       <c r="Q7">
-        <v>59.24561684666666</v>
+        <v>59.20940688266667</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1646617065174273</v>
+        <v>0.1655603261800496</v>
       </c>
       <c r="T7">
-        <v>0.8287564206637427</v>
+        <v>0.8350219946400319</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>241.5173164307298</v>
+        <v>201.2644303589415</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1577393066092466</v>
+        <v>0.1572894920269373</v>
       </c>
       <c r="C8">
-        <v>97.90853258359226</v>
+        <v>97.05323753038834</v>
       </c>
       <c r="D8">
-        <v>82.97893258359225</v>
+        <v>83.15203753038834</v>
       </c>
       <c r="E8">
-        <v>0.5304000000000002</v>
+        <v>1.5588</v>
       </c>
       <c r="F8">
-        <v>6.1704</v>
+        <v>7.198799999999999</v>
       </c>
       <c r="G8">
         <v>21.1</v>
@@ -1943,28 +1943,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M8">
-        <v>0.31037112</v>
+        <v>0.3620996399999999</v>
       </c>
       <c r="N8">
-        <v>62.15629554666667</v>
+        <v>62.10456702666667</v>
       </c>
       <c r="O8">
-        <v>18.646888664</v>
+        <v>18.631370108</v>
       </c>
       <c r="P8">
-        <v>43.50940688266667</v>
+        <v>43.47319691866667</v>
       </c>
       <c r="Q8">
-        <v>59.20940688266667</v>
+        <v>59.17319691866668</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1655603261800496</v>
+        <v>0.1664782709967068</v>
       </c>
       <c r="T8">
-        <v>0.8350219946400319</v>
+        <v>0.841422312142693</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>201.2644303589415</v>
+        <v>172.5123688790927</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1572894920269374</v>
+        <v>0.1568396774446281</v>
       </c>
       <c r="C9">
-        <v>97.05323753038834</v>
+        <v>96.19866622630839</v>
       </c>
       <c r="D9">
-        <v>83.15203753038834</v>
+        <v>83.32586622630839</v>
       </c>
       <c r="E9">
-        <v>1.558800000000002</v>
+        <v>2.5872</v>
       </c>
       <c r="F9">
-        <v>7.198800000000001</v>
+        <v>8.2272</v>
       </c>
       <c r="G9">
         <v>21.1</v>
@@ -2025,28 +2025,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M9">
-        <v>0.3620996400000001</v>
+        <v>0.4138281599999999</v>
       </c>
       <c r="N9">
-        <v>62.10456702666667</v>
+        <v>62.05283850666667</v>
       </c>
       <c r="O9">
-        <v>18.631370108</v>
+        <v>18.615851552</v>
       </c>
       <c r="P9">
-        <v>43.47319691866667</v>
+        <v>43.43698695466666</v>
       </c>
       <c r="Q9">
-        <v>59.17319691866668</v>
+        <v>59.13698695466667</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1664782709967068</v>
+        <v>0.1674161711354653</v>
       </c>
       <c r="T9">
-        <v>0.841422312142693</v>
+        <v>0.8479617669823685</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>172.5123688790927</v>
+        <v>150.9483227692061</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1568396774446281</v>
+        <v>0.1563898628623188</v>
       </c>
       <c r="C10">
-        <v>96.19866622630839</v>
+        <v>95.34482321983693</v>
       </c>
       <c r="D10">
-        <v>83.32586622630839</v>
+        <v>83.50042321983692</v>
       </c>
       <c r="E10">
-        <v>2.5872</v>
+        <v>3.6156</v>
       </c>
       <c r="F10">
-        <v>8.2272</v>
+        <v>9.255599999999999</v>
       </c>
       <c r="G10">
         <v>21.1</v>
@@ -2107,28 +2107,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M10">
-        <v>0.4138281599999999</v>
+        <v>0.4655566799999999</v>
       </c>
       <c r="N10">
-        <v>62.05283850666667</v>
+        <v>62.00110998666667</v>
       </c>
       <c r="O10">
-        <v>18.615851552</v>
+        <v>18.600332996</v>
       </c>
       <c r="P10">
-        <v>43.43698695466666</v>
+        <v>43.40077699066667</v>
       </c>
       <c r="Q10">
-        <v>59.13698695466667</v>
+        <v>59.10077699066667</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1674161711354653</v>
+        <v>0.1683746844640865</v>
       </c>
       <c r="T10">
-        <v>0.8479617669823685</v>
+        <v>0.8546449461042345</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>150.9483227692061</v>
+        <v>134.176286905961</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1563898628623188</v>
+        <v>0.1559400482800094</v>
       </c>
       <c r="C11">
-        <v>95.34482321983693</v>
+        <v>94.49171309765245</v>
       </c>
       <c r="D11">
-        <v>83.50042321983692</v>
+        <v>83.67571309765245</v>
       </c>
       <c r="E11">
-        <v>3.6156</v>
+        <v>4.643999999999999</v>
       </c>
       <c r="F11">
-        <v>9.255599999999999</v>
+        <v>10.284</v>
       </c>
       <c r="G11">
         <v>21.1</v>
@@ -2189,28 +2189,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M11">
-        <v>0.4655566799999999</v>
+        <v>0.5172851999999999</v>
       </c>
       <c r="N11">
-        <v>62.00110998666667</v>
+        <v>61.94938146666667</v>
       </c>
       <c r="O11">
-        <v>18.600332996</v>
+        <v>18.58481444</v>
       </c>
       <c r="P11">
-        <v>43.40077699066667</v>
+        <v>43.36456702666666</v>
       </c>
       <c r="Q11">
-        <v>59.10077699066667</v>
+        <v>59.06456702666667</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1683746844640865</v>
+        <v>0.1693544980888994</v>
       </c>
       <c r="T11">
-        <v>0.8546449461042345</v>
+        <v>0.8614766403176976</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>134.176286905961</v>
+        <v>120.7586582153649</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1559400482800094</v>
+        <v>0.1554902336977002</v>
       </c>
       <c r="C12">
-        <v>94.49171309765244</v>
+        <v>93.63934048502918</v>
       </c>
       <c r="D12">
-        <v>83.67571309765245</v>
+        <v>83.85174048502918</v>
       </c>
       <c r="E12">
-        <v>4.644000000000001</v>
+        <v>5.672400000000001</v>
       </c>
       <c r="F12">
-        <v>10.284</v>
+        <v>11.3124</v>
       </c>
       <c r="G12">
         <v>21.1</v>
@@ -2271,28 +2271,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M12">
-        <v>0.5172852</v>
+        <v>0.5690137199999999</v>
       </c>
       <c r="N12">
-        <v>61.94938146666667</v>
+        <v>61.89765294666667</v>
       </c>
       <c r="O12">
-        <v>18.58481444</v>
+        <v>18.569295884</v>
       </c>
       <c r="P12">
-        <v>43.36456702666666</v>
+        <v>43.32835706266667</v>
       </c>
       <c r="Q12">
-        <v>59.06456702666667</v>
+        <v>59.02835706266667</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1693544980888994</v>
+        <v>0.1703563299974159</v>
       </c>
       <c r="T12">
-        <v>0.8614766403176976</v>
+        <v>0.8684618557494408</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>120.7586582153649</v>
+        <v>109.7805983776044</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1554902336977002</v>
+        <v>0.1550404191153908</v>
       </c>
       <c r="C13">
-        <v>93.63934048502918</v>
+        <v>92.78771004624392</v>
       </c>
       <c r="D13">
-        <v>83.85174048502918</v>
+        <v>84.02851004624391</v>
       </c>
       <c r="E13">
-        <v>5.672400000000001</v>
+        <v>6.7008</v>
       </c>
       <c r="F13">
-        <v>11.3124</v>
+        <v>12.3408</v>
       </c>
       <c r="G13">
         <v>21.1</v>
@@ -2353,28 +2353,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M13">
-        <v>0.5690137199999999</v>
+        <v>0.62074224</v>
       </c>
       <c r="N13">
-        <v>61.89765294666667</v>
+        <v>61.84592442666667</v>
       </c>
       <c r="O13">
-        <v>18.569295884</v>
+        <v>18.553777328</v>
       </c>
       <c r="P13">
-        <v>43.32835706266667</v>
+        <v>43.29214709866667</v>
       </c>
       <c r="Q13">
-        <v>59.02835706266667</v>
+        <v>58.99214709866668</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1703563299974159</v>
+        <v>0.1713809308129441</v>
       </c>
       <c r="T13">
-        <v>0.8684618557494408</v>
+        <v>0.8756058260773599</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>109.7805983776044</v>
+        <v>100.6322151794707</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1550404191153908</v>
+        <v>0.1545906045330815</v>
       </c>
       <c r="C14">
-        <v>92.78771004624392</v>
+        <v>91.93682648498788</v>
       </c>
       <c r="D14">
-        <v>84.02851004624391</v>
+        <v>84.20602648498789</v>
       </c>
       <c r="E14">
-        <v>6.7008</v>
+        <v>7.729200000000001</v>
       </c>
       <c r="F14">
-        <v>12.3408</v>
+        <v>13.3692</v>
       </c>
       <c r="G14">
         <v>21.1</v>
@@ -2435,28 +2435,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M14">
-        <v>0.62074224</v>
+        <v>0.6724707600000001</v>
       </c>
       <c r="N14">
-        <v>61.84592442666667</v>
+        <v>61.79419590666667</v>
       </c>
       <c r="O14">
-        <v>18.553777328</v>
+        <v>18.538258772</v>
       </c>
       <c r="P14">
-        <v>43.29214709866667</v>
+        <v>43.25593713466667</v>
       </c>
       <c r="Q14">
-        <v>58.99214709866668</v>
+        <v>58.95593713466667</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1713809308129441</v>
+        <v>0.1724290856702086</v>
       </c>
       <c r="T14">
-        <v>0.8756058260773599</v>
+        <v>0.8829140256082197</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>100.6322151794707</v>
+        <v>92.89127555028067</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1545906045330815</v>
+        <v>0.1541407899507722</v>
       </c>
       <c r="C15">
-        <v>91.93682648498788</v>
+        <v>91.08669454478412</v>
       </c>
       <c r="D15">
-        <v>84.20602648498789</v>
+        <v>84.38429454478411</v>
       </c>
       <c r="E15">
-        <v>7.729200000000001</v>
+        <v>8.757600000000004</v>
       </c>
       <c r="F15">
-        <v>13.3692</v>
+        <v>14.3976</v>
       </c>
       <c r="G15">
         <v>21.1</v>
@@ -2517,28 +2517,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M15">
-        <v>0.6724707600000001</v>
+        <v>0.7241992800000001</v>
       </c>
       <c r="N15">
-        <v>61.79419590666667</v>
+        <v>61.74246738666667</v>
       </c>
       <c r="O15">
-        <v>18.538258772</v>
+        <v>18.522740216</v>
       </c>
       <c r="P15">
-        <v>43.25593713466667</v>
+        <v>43.21972717066667</v>
       </c>
       <c r="Q15">
-        <v>58.95593713466667</v>
+        <v>58.91972717066668</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1724290856702086</v>
+        <v>0.1735016162218282</v>
       </c>
       <c r="T15">
-        <v>0.8829140256082197</v>
+        <v>0.8903921832677042</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>92.89127555028067</v>
+        <v>86.25618443954633</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1541407899507722</v>
+        <v>0.1536909753684629</v>
       </c>
       <c r="C16">
-        <v>91.08669454478412</v>
+        <v>90.23731900940989</v>
       </c>
       <c r="D16">
-        <v>84.38429454478411</v>
+        <v>84.56331900940988</v>
       </c>
       <c r="E16">
-        <v>8.757600000000004</v>
+        <v>9.786000000000001</v>
       </c>
       <c r="F16">
-        <v>14.3976</v>
+        <v>15.426</v>
       </c>
       <c r="G16">
         <v>21.1</v>
@@ -2599,28 +2599,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M16">
-        <v>0.7241992800000001</v>
+        <v>0.7759278000000001</v>
       </c>
       <c r="N16">
-        <v>61.74246738666667</v>
+        <v>61.69073886666667</v>
       </c>
       <c r="O16">
-        <v>18.522740216</v>
+        <v>18.50722166</v>
       </c>
       <c r="P16">
-        <v>43.21972717066667</v>
+        <v>43.18351720666667</v>
       </c>
       <c r="Q16">
-        <v>58.91972717066668</v>
+        <v>58.88351720666667</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1735016162218282</v>
+        <v>0.1745993827864269</v>
       </c>
       <c r="T16">
-        <v>0.8903921832677042</v>
+        <v>0.8980462975780001</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>86.25618443954633</v>
+        <v>80.50577214357659</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1536909753684629</v>
+        <v>0.1532411607861536</v>
       </c>
       <c r="C17">
-        <v>90.23731900940989</v>
+        <v>89.38870470332463</v>
       </c>
       <c r="D17">
-        <v>84.56331900940988</v>
+        <v>84.74310470332462</v>
       </c>
       <c r="E17">
-        <v>9.786000000000001</v>
+        <v>10.8144</v>
       </c>
       <c r="F17">
-        <v>15.426</v>
+        <v>16.4544</v>
       </c>
       <c r="G17">
         <v>21.1</v>
@@ -2681,28 +2681,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M17">
-        <v>0.7759277999999999</v>
+        <v>0.8276563199999999</v>
       </c>
       <c r="N17">
-        <v>61.69073886666667</v>
+        <v>61.63901034666667</v>
       </c>
       <c r="O17">
-        <v>18.50722166</v>
+        <v>18.491703104</v>
       </c>
       <c r="P17">
-        <v>43.18351720666667</v>
+        <v>43.14730724266667</v>
       </c>
       <c r="Q17">
-        <v>58.88351720666667</v>
+        <v>58.84730724266667</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1745993827864269</v>
+        <v>0.1757232866501829</v>
       </c>
       <c r="T17">
-        <v>0.8980462975780001</v>
+        <v>0.9058826527052077</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>80.50577214357659</v>
+        <v>75.47416138460306</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1532411607861536</v>
+        <v>0.1527913462038443</v>
       </c>
       <c r="C18">
-        <v>89.38870470332463</v>
+        <v>88.54085649210322</v>
       </c>
       <c r="D18">
-        <v>84.74310470332462</v>
+        <v>84.92365649210322</v>
       </c>
       <c r="E18">
-        <v>10.8144</v>
+        <v>11.8428</v>
       </c>
       <c r="F18">
-        <v>16.4544</v>
+        <v>17.4828</v>
       </c>
       <c r="G18">
         <v>21.1</v>
@@ -2763,28 +2763,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M18">
-        <v>0.8276563199999999</v>
+        <v>0.8793848400000001</v>
       </c>
       <c r="N18">
-        <v>61.63901034666667</v>
+        <v>61.58728182666667</v>
       </c>
       <c r="O18">
-        <v>18.491703104</v>
+        <v>18.476184548</v>
       </c>
       <c r="P18">
-        <v>43.14730724266667</v>
+        <v>43.11109727866667</v>
       </c>
       <c r="Q18">
-        <v>58.84730724266667</v>
+        <v>58.81109727866667</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1757232866501829</v>
+        <v>0.1768742725347522</v>
       </c>
       <c r="T18">
-        <v>0.9058826527052077</v>
+        <v>0.9139078356668061</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>75.47416138460306</v>
+        <v>71.03450483256758</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1527913462038443</v>
+        <v>0.152341531621535</v>
       </c>
       <c r="C19">
-        <v>88.54085649210322</v>
+        <v>87.69377928287525</v>
       </c>
       <c r="D19">
-        <v>84.92365649210322</v>
+        <v>85.10497928287526</v>
       </c>
       <c r="E19">
-        <v>11.8428</v>
+        <v>12.8712</v>
       </c>
       <c r="F19">
-        <v>17.4828</v>
+        <v>18.5112</v>
       </c>
       <c r="G19">
         <v>21.1</v>
@@ -2845,28 +2845,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M19">
-        <v>0.8793848400000001</v>
+        <v>0.9311133600000001</v>
       </c>
       <c r="N19">
-        <v>61.58728182666667</v>
+        <v>61.53555330666667</v>
       </c>
       <c r="O19">
-        <v>18.476184548</v>
+        <v>18.460665992</v>
       </c>
       <c r="P19">
-        <v>43.11109727866667</v>
+        <v>43.07488731466667</v>
       </c>
       <c r="Q19">
-        <v>58.81109727866667</v>
+        <v>58.77488731466667</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1768742725347522</v>
+        <v>0.1780533312457744</v>
       </c>
       <c r="T19">
-        <v>0.9139078356668061</v>
+        <v>0.9221287547981992</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>71.03450483256758</v>
+        <v>67.08814345298049</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.152341531621535</v>
+        <v>0.1518917170392257</v>
       </c>
       <c r="C20">
-        <v>87.69377928287525</v>
+        <v>86.84747802476915</v>
       </c>
       <c r="D20">
-        <v>85.10497928287526</v>
+        <v>85.28707802476914</v>
       </c>
       <c r="E20">
-        <v>12.8712</v>
+        <v>13.8996</v>
       </c>
       <c r="F20">
-        <v>18.5112</v>
+        <v>19.5396</v>
       </c>
       <c r="G20">
         <v>21.1</v>
@@ -2927,28 +2927,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M20">
-        <v>0.9311133599999999</v>
+        <v>0.9828418799999999</v>
       </c>
       <c r="N20">
-        <v>61.53555330666667</v>
+        <v>61.48382478666667</v>
       </c>
       <c r="O20">
-        <v>18.460665992</v>
+        <v>18.445147436</v>
       </c>
       <c r="P20">
-        <v>43.07488731466667</v>
+        <v>43.03867735066667</v>
       </c>
       <c r="Q20">
-        <v>58.77488731466667</v>
+        <v>58.73867735066666</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1780533312457744</v>
+        <v>0.1792615025175626</v>
       </c>
       <c r="T20">
-        <v>0.9221287547981992</v>
+        <v>0.9305526595871578</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>67.0881434529805</v>
+        <v>63.55718853440257</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1518917170392257</v>
+        <v>0.1514419024569164</v>
       </c>
       <c r="C21">
-        <v>86.84747802476915</v>
+        <v>86.0019577093628</v>
       </c>
       <c r="D21">
-        <v>85.28707802476914</v>
+        <v>85.4699577093628</v>
       </c>
       <c r="E21">
-        <v>13.8996</v>
+        <v>14.928</v>
       </c>
       <c r="F21">
-        <v>19.5396</v>
+        <v>20.568</v>
       </c>
       <c r="G21">
         <v>21.1</v>
@@ -3009,28 +3009,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M21">
-        <v>0.9828418799999999</v>
+        <v>1.0345704</v>
       </c>
       <c r="N21">
-        <v>61.48382478666667</v>
+        <v>61.43209626666667</v>
       </c>
       <c r="O21">
-        <v>18.445147436</v>
+        <v>18.42962888</v>
       </c>
       <c r="P21">
-        <v>43.03867735066667</v>
+        <v>43.00246738666667</v>
       </c>
       <c r="Q21">
-        <v>58.73867735066666</v>
+        <v>58.70246738666667</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1792615025175626</v>
+        <v>0.1804998780711455</v>
       </c>
       <c r="T21">
-        <v>0.9305526595871578</v>
+        <v>0.9391871619958404</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>63.55718853440257</v>
+        <v>60.37932910768244</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1514419024569164</v>
+        <v>0.1509920878746071</v>
       </c>
       <c r="C22">
-        <v>86.0019577093628</v>
+        <v>85.15722337113944</v>
       </c>
       <c r="D22">
-        <v>85.4699577093628</v>
+        <v>85.65362337113943</v>
       </c>
       <c r="E22">
-        <v>14.928</v>
+        <v>15.9564</v>
       </c>
       <c r="F22">
-        <v>20.568</v>
+        <v>21.5964</v>
       </c>
       <c r="G22">
         <v>21.1</v>
@@ -3091,28 +3091,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M22">
-        <v>1.0345704</v>
+        <v>1.08629892</v>
       </c>
       <c r="N22">
-        <v>61.43209626666667</v>
+        <v>61.38036774666667</v>
       </c>
       <c r="O22">
-        <v>18.42962888</v>
+        <v>18.414110324</v>
       </c>
       <c r="P22">
-        <v>43.00246738666667</v>
+        <v>42.96625742266667</v>
       </c>
       <c r="Q22">
-        <v>58.70246738666667</v>
+        <v>58.66625742266667</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1804998780711455</v>
+        <v>0.1817696049045659</v>
       </c>
       <c r="T22">
-        <v>0.9391871619958404</v>
+        <v>0.9480402594022111</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>60.37932910768244</v>
+        <v>57.50412295969756</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1509920878746071</v>
+        <v>0.1505422732922978</v>
       </c>
       <c r="C23">
-        <v>85.15722337113944</v>
+        <v>84.31328008794981</v>
       </c>
       <c r="D23">
-        <v>85.65362337113945</v>
+        <v>85.83808008794979</v>
       </c>
       <c r="E23">
-        <v>15.9564</v>
+        <v>16.9848</v>
       </c>
       <c r="F23">
-        <v>21.5964</v>
+        <v>22.6248</v>
       </c>
       <c r="G23">
         <v>21.1</v>
@@ -3173,28 +3173,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M23">
-        <v>1.08629892</v>
+        <v>1.13802744</v>
       </c>
       <c r="N23">
-        <v>61.38036774666667</v>
+        <v>61.32863922666667</v>
       </c>
       <c r="O23">
-        <v>18.414110324</v>
+        <v>18.398591768</v>
       </c>
       <c r="P23">
-        <v>42.96625742266667</v>
+        <v>42.93004745866666</v>
       </c>
       <c r="Q23">
-        <v>58.66625742266667</v>
+        <v>58.63004745866667</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1817696049045659</v>
+        <v>0.1830718888362792</v>
       </c>
       <c r="T23">
-        <v>0.948040259402211</v>
+        <v>0.957120359306181</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>57.50412295969757</v>
+        <v>54.89029918880222</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1505422732922978</v>
+        <v>0.1500924587099884</v>
       </c>
       <c r="C24">
-        <v>84.31328008794981</v>
+        <v>83.47013298148002</v>
       </c>
       <c r="D24">
-        <v>85.83808008794979</v>
+        <v>86.02333298148001</v>
       </c>
       <c r="E24">
-        <v>16.9848</v>
+        <v>18.0132</v>
       </c>
       <c r="F24">
-        <v>22.6248</v>
+        <v>23.6532</v>
       </c>
       <c r="G24">
         <v>21.1</v>
@@ -3255,28 +3255,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M24">
-        <v>1.13802744</v>
+        <v>1.18975596</v>
       </c>
       <c r="N24">
-        <v>61.32863922666667</v>
+        <v>61.27691070666667</v>
       </c>
       <c r="O24">
-        <v>18.398591768</v>
+        <v>18.383073212</v>
       </c>
       <c r="P24">
-        <v>42.93004745866666</v>
+        <v>42.89383749466667</v>
       </c>
       <c r="Q24">
-        <v>58.63004745866667</v>
+        <v>58.59383749466667</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1830718888362792</v>
+        <v>0.1844079983246603</v>
       </c>
       <c r="T24">
-        <v>0.957120359306181</v>
+        <v>0.9664363059609035</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>54.89029918880222</v>
+        <v>52.50376444146299</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1500924587099884</v>
+        <v>0.1496426441276791</v>
       </c>
       <c r="C25">
-        <v>83.47013298148002</v>
+        <v>82.62778721772557</v>
       </c>
       <c r="D25">
-        <v>86.02333298148001</v>
+        <v>86.20938721772556</v>
       </c>
       <c r="E25">
-        <v>18.0132</v>
+        <v>19.0416</v>
       </c>
       <c r="F25">
-        <v>23.6532</v>
+        <v>24.6816</v>
       </c>
       <c r="G25">
         <v>21.1</v>
@@ -3337,28 +3337,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M25">
-        <v>1.18975596</v>
+        <v>1.24148448</v>
       </c>
       <c r="N25">
-        <v>61.27691070666667</v>
+        <v>61.22518218666667</v>
       </c>
       <c r="O25">
-        <v>18.383073212</v>
+        <v>18.367554656</v>
       </c>
       <c r="P25">
-        <v>42.89383749466667</v>
+        <v>42.85762753066668</v>
       </c>
       <c r="Q25">
-        <v>58.59383749466667</v>
+        <v>58.55762753066668</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1844079983246603</v>
+        <v>0.1857792685890515</v>
       </c>
       <c r="T25">
-        <v>0.9664363059609035</v>
+        <v>0.9759974091065396</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>52.50376444146299</v>
+        <v>50.31610758973537</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1496426441276791</v>
+        <v>0.1491928295453698</v>
       </c>
       <c r="C26">
-        <v>82.62778721772557</v>
+        <v>81.78624800747167</v>
       </c>
       <c r="D26">
-        <v>86.20938721772556</v>
+        <v>86.39624800747168</v>
       </c>
       <c r="E26">
-        <v>19.0416</v>
+        <v>20.07</v>
       </c>
       <c r="F26">
-        <v>24.6816</v>
+        <v>25.71</v>
       </c>
       <c r="G26">
         <v>21.1</v>
@@ -3419,28 +3419,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M26">
-        <v>1.24148448</v>
+        <v>1.293213</v>
       </c>
       <c r="N26">
-        <v>61.22518218666667</v>
+        <v>61.17345366666667</v>
       </c>
       <c r="O26">
-        <v>18.367554656</v>
+        <v>18.3520361</v>
       </c>
       <c r="P26">
-        <v>42.85762753066668</v>
+        <v>42.82141756666667</v>
       </c>
       <c r="Q26">
-        <v>58.55762753066668</v>
+        <v>58.52141756666667</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1857792685890515</v>
+        <v>0.1871871060604931</v>
       </c>
       <c r="T26">
-        <v>0.9759974091065396</v>
+        <v>0.9858134750027262</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>50.31610758973537</v>
+        <v>48.30346328614596</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1491928295453698</v>
+        <v>0.1487430149630605</v>
       </c>
       <c r="C27">
-        <v>81.78624800747167</v>
+        <v>80.94552060677965</v>
       </c>
       <c r="D27">
-        <v>86.39624800747168</v>
+        <v>86.58392060677964</v>
       </c>
       <c r="E27">
-        <v>20.07</v>
+        <v>21.0984</v>
       </c>
       <c r="F27">
-        <v>25.71</v>
+        <v>26.7384</v>
       </c>
       <c r="G27">
         <v>21.1</v>
@@ -3501,28 +3501,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M27">
-        <v>1.293213</v>
+        <v>1.34494152</v>
       </c>
       <c r="N27">
-        <v>61.17345366666667</v>
+        <v>61.12172514666667</v>
       </c>
       <c r="O27">
-        <v>18.3520361</v>
+        <v>18.336517544</v>
       </c>
       <c r="P27">
-        <v>42.82141756666667</v>
+        <v>42.78520760266667</v>
       </c>
       <c r="Q27">
-        <v>58.52141756666667</v>
+        <v>58.48520760266668</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1871871060604931</v>
+        <v>0.188632993193325</v>
       </c>
       <c r="T27">
-        <v>0.9858134750027262</v>
+        <v>0.9958948399771879</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>48.30346328614596</v>
+        <v>46.44563777514034</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1487430149630605</v>
+        <v>0.1482932003807512</v>
       </c>
       <c r="C28">
-        <v>80.94552060677965</v>
+        <v>80.10561031747967</v>
       </c>
       <c r="D28">
-        <v>86.58392060677964</v>
+        <v>86.77241031747968</v>
       </c>
       <c r="E28">
-        <v>21.0984</v>
+        <v>22.1268</v>
       </c>
       <c r="F28">
-        <v>26.7384</v>
+        <v>27.7668</v>
       </c>
       <c r="G28">
         <v>21.1</v>
@@ -3583,28 +3583,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M28">
-        <v>1.34494152</v>
+        <v>1.39667004</v>
       </c>
       <c r="N28">
-        <v>61.12172514666667</v>
+        <v>61.06999662666666</v>
       </c>
       <c r="O28">
-        <v>18.336517544</v>
+        <v>18.320998988</v>
       </c>
       <c r="P28">
-        <v>42.78520760266667</v>
+        <v>42.74899763866667</v>
       </c>
       <c r="Q28">
-        <v>58.48520760266668</v>
+        <v>58.44899763866667</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.188632993193325</v>
+        <v>0.190118493672262</v>
       </c>
       <c r="T28">
-        <v>0.9958948399771879</v>
+        <v>1.006252406731772</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>46.44563777514034</v>
+        <v>44.72542896865366</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1482932003807512</v>
+        <v>0.1478433857984419</v>
       </c>
       <c r="C29">
-        <v>80.10561031747967</v>
+        <v>79.26652248767031</v>
       </c>
       <c r="D29">
-        <v>86.77241031747968</v>
+        <v>86.96172248767031</v>
       </c>
       <c r="E29">
-        <v>22.1268</v>
+        <v>23.1552</v>
       </c>
       <c r="F29">
-        <v>27.7668</v>
+        <v>28.7952</v>
       </c>
       <c r="G29">
         <v>21.1</v>
@@ -3665,28 +3665,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M29">
-        <v>1.39667004</v>
+        <v>1.44839856</v>
       </c>
       <c r="N29">
-        <v>61.06999662666666</v>
+        <v>61.01826810666667</v>
       </c>
       <c r="O29">
-        <v>18.320998988</v>
+        <v>18.305480432</v>
       </c>
       <c r="P29">
-        <v>42.74899763866667</v>
+        <v>42.71278767466667</v>
       </c>
       <c r="Q29">
-        <v>58.44899763866667</v>
+        <v>58.41278767466667</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.190118493672262</v>
+        <v>0.1916452580533915</v>
       </c>
       <c r="T29">
-        <v>1.006252406731772</v>
+        <v>1.016897683673983</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>44.72542896865366</v>
+        <v>43.12809221977317</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1478433857984419</v>
+        <v>0.1473935712161326</v>
       </c>
       <c r="C30">
-        <v>79.26652248767031</v>
+        <v>78.42826251222391</v>
       </c>
       <c r="D30">
-        <v>86.96172248767031</v>
+        <v>87.15186251222391</v>
       </c>
       <c r="E30">
-        <v>23.1552</v>
+        <v>24.18360000000001</v>
       </c>
       <c r="F30">
-        <v>28.7952</v>
+        <v>29.82360000000001</v>
       </c>
       <c r="G30">
         <v>21.1</v>
@@ -3747,28 +3747,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M30">
-        <v>1.44839856</v>
+        <v>1.50012708</v>
       </c>
       <c r="N30">
-        <v>61.01826810666667</v>
+        <v>60.96653958666667</v>
       </c>
       <c r="O30">
-        <v>18.305480432</v>
+        <v>18.289961876</v>
       </c>
       <c r="P30">
-        <v>42.71278767466667</v>
+        <v>42.67657771066667</v>
       </c>
       <c r="Q30">
-        <v>58.41278767466667</v>
+        <v>58.37657771066667</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1916452580533915</v>
+        <v>0.1932150298818769</v>
       </c>
       <c r="T30">
-        <v>1.016897683673983</v>
+        <v>1.027842827572313</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>43.12809221977317</v>
+        <v>41.64091662598789</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1473935712161326</v>
+        <v>0.1469437566338233</v>
       </c>
       <c r="C31">
-        <v>78.42826251222391</v>
+        <v>77.59083583329951</v>
       </c>
       <c r="D31">
-        <v>87.15186251222391</v>
+        <v>87.34283583329952</v>
       </c>
       <c r="E31">
-        <v>24.1836</v>
+        <v>25.212</v>
       </c>
       <c r="F31">
-        <v>29.8236</v>
+        <v>30.852</v>
       </c>
       <c r="G31">
         <v>21.1</v>
@@ -3829,28 +3829,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M31">
-        <v>1.50012708</v>
+        <v>1.5518556</v>
       </c>
       <c r="N31">
-        <v>60.96653958666667</v>
+        <v>60.91481106666667</v>
       </c>
       <c r="O31">
-        <v>18.289961876</v>
+        <v>18.27444332</v>
       </c>
       <c r="P31">
-        <v>42.67657771066667</v>
+        <v>42.64036774666667</v>
       </c>
       <c r="Q31">
-        <v>58.37657771066667</v>
+        <v>58.34036774666667</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1932150298818769</v>
+        <v>0.1948296523340333</v>
       </c>
       <c r="T31">
-        <v>1.027842827572313</v>
+        <v>1.039100689867738</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>41.64091662598789</v>
+        <v>40.2528860717883</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1469437566338233</v>
+        <v>0.146493942051514</v>
       </c>
       <c r="C32">
-        <v>77.59083583329951</v>
+        <v>76.75424794086183</v>
       </c>
       <c r="D32">
-        <v>87.34283583329952</v>
+        <v>87.53464794086183</v>
       </c>
       <c r="E32">
-        <v>25.212</v>
+        <v>26.2404</v>
       </c>
       <c r="F32">
-        <v>30.852</v>
+        <v>31.8804</v>
       </c>
       <c r="G32">
         <v>21.1</v>
@@ -3911,28 +3911,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M32">
-        <v>1.5518556</v>
+        <v>1.60358412</v>
       </c>
       <c r="N32">
-        <v>60.91481106666667</v>
+        <v>60.86308254666667</v>
       </c>
       <c r="O32">
-        <v>18.27444332</v>
+        <v>18.258924764</v>
       </c>
       <c r="P32">
-        <v>42.64036774666667</v>
+        <v>42.60415778266667</v>
       </c>
       <c r="Q32">
-        <v>58.34036774666667</v>
+        <v>58.30415778266666</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1948296523340333</v>
+        <v>0.1964910754369768</v>
       </c>
       <c r="T32">
-        <v>1.039100689867738</v>
+        <v>1.050684867012306</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>40.2528860717883</v>
+        <v>38.95440587592415</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.146493942051514</v>
+        <v>0.1460441274692047</v>
       </c>
       <c r="C33">
-        <v>76.75424794086183</v>
+        <v>75.91850437320734</v>
       </c>
       <c r="D33">
-        <v>87.53464794086183</v>
+        <v>87.72730437320733</v>
       </c>
       <c r="E33">
-        <v>26.2404</v>
+        <v>27.2688</v>
       </c>
       <c r="F33">
-        <v>31.8804</v>
+        <v>32.9088</v>
       </c>
       <c r="G33">
         <v>21.1</v>
@@ -3993,28 +3993,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M33">
-        <v>1.60358412</v>
+        <v>1.65531264</v>
       </c>
       <c r="N33">
-        <v>60.86308254666667</v>
+        <v>60.81135402666667</v>
       </c>
       <c r="O33">
-        <v>18.258924764</v>
+        <v>18.243406208</v>
       </c>
       <c r="P33">
-        <v>42.60415778266667</v>
+        <v>42.56794781866667</v>
       </c>
       <c r="Q33">
-        <v>58.30415778266666</v>
+        <v>58.26794781866667</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1964910754369768</v>
+        <v>0.198201363925301</v>
       </c>
       <c r="T33">
-        <v>1.050684867012306</v>
+        <v>1.062609755249361</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>38.95440587592415</v>
+        <v>37.73708069230153</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1460441274692047</v>
+        <v>0.1455943128868954</v>
       </c>
       <c r="C34">
-        <v>75.91850437320734</v>
+        <v>75.08361071749748</v>
       </c>
       <c r="D34">
-        <v>87.72730437320733</v>
+        <v>87.92081071749749</v>
       </c>
       <c r="E34">
-        <v>27.2688</v>
+        <v>28.2972</v>
       </c>
       <c r="F34">
-        <v>32.9088</v>
+        <v>33.9372</v>
       </c>
       <c r="G34">
         <v>21.1</v>
@@ -4075,28 +4075,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M34">
-        <v>1.65531264</v>
+        <v>1.70704116</v>
       </c>
       <c r="N34">
-        <v>60.81135402666667</v>
+        <v>60.75962550666667</v>
       </c>
       <c r="O34">
-        <v>18.243406208</v>
+        <v>18.227887652</v>
       </c>
       <c r="P34">
-        <v>42.56794781866667</v>
+        <v>42.53173785466667</v>
       </c>
       <c r="Q34">
-        <v>58.26794781866667</v>
+        <v>58.23173785466666</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.198201363925301</v>
+        <v>0.1999627058013364</v>
       </c>
       <c r="T34">
-        <v>1.062609755249361</v>
+        <v>1.074890610299463</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>37.73708069230153</v>
+        <v>36.59353279253481</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1455943128868954</v>
+        <v>0.145144498304586</v>
       </c>
       <c r="C35">
-        <v>75.08361071749748</v>
+        <v>74.2495726102986</v>
       </c>
       <c r="D35">
-        <v>87.92081071749749</v>
+        <v>88.11517261029859</v>
       </c>
       <c r="E35">
-        <v>28.2972</v>
+        <v>29.3256</v>
       </c>
       <c r="F35">
-        <v>33.9372</v>
+        <v>34.9656</v>
       </c>
       <c r="G35">
         <v>21.1</v>
@@ -4157,28 +4157,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M35">
-        <v>1.70704116</v>
+        <v>1.75876968</v>
       </c>
       <c r="N35">
-        <v>60.75962550666667</v>
+        <v>60.70789698666667</v>
       </c>
       <c r="O35">
-        <v>18.227887652</v>
+        <v>18.212369096</v>
       </c>
       <c r="P35">
-        <v>42.53173785466667</v>
+        <v>42.49552789066666</v>
       </c>
       <c r="Q35">
-        <v>58.23173785466666</v>
+        <v>58.19552789066667</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1999627058013364</v>
+        <v>0.2017774216736152</v>
       </c>
       <c r="T35">
-        <v>1.074890610299463</v>
+        <v>1.087543612472295</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>36.59353279253481</v>
+        <v>35.51725241628379</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.145144498304586</v>
+        <v>0.1446946837222767</v>
       </c>
       <c r="C36">
-        <v>74.2495726102986</v>
+        <v>73.41639573812921</v>
       </c>
       <c r="D36">
-        <v>88.11517261029859</v>
+        <v>88.31039573812922</v>
       </c>
       <c r="E36">
-        <v>29.3256</v>
+        <v>30.35400000000001</v>
       </c>
       <c r="F36">
-        <v>34.9656</v>
+        <v>35.99400000000001</v>
       </c>
       <c r="G36">
         <v>21.1</v>
@@ -4239,28 +4239,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M36">
-        <v>1.75876968</v>
+        <v>1.8104982</v>
       </c>
       <c r="N36">
-        <v>60.70789698666667</v>
+        <v>60.65616846666667</v>
       </c>
       <c r="O36">
-        <v>18.212369096</v>
+        <v>18.19685054</v>
       </c>
       <c r="P36">
-        <v>42.49552789066666</v>
+        <v>42.45931792666667</v>
       </c>
       <c r="Q36">
-        <v>58.19552789066667</v>
+        <v>58.15931792666667</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2017774216736152</v>
+        <v>0.2036479749573488</v>
       </c>
       <c r="T36">
-        <v>1.087543612472295</v>
+        <v>1.100585937788906</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>35.51725241628379</v>
+        <v>34.50247377581854</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1446946837222767</v>
+        <v>0.1442448691399675</v>
       </c>
       <c r="C37">
-        <v>73.41639573812921</v>
+        <v>72.58408583801483</v>
       </c>
       <c r="D37">
-        <v>88.31039573812922</v>
+        <v>88.50648583801484</v>
       </c>
       <c r="E37">
-        <v>30.35400000000001</v>
+        <v>31.3824</v>
       </c>
       <c r="F37">
-        <v>35.99400000000001</v>
+        <v>37.0224</v>
       </c>
       <c r="G37">
         <v>21.1</v>
@@ -4321,28 +4321,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M37">
-        <v>1.8104982</v>
+        <v>1.86222672</v>
       </c>
       <c r="N37">
-        <v>60.65616846666667</v>
+        <v>60.60443994666667</v>
       </c>
       <c r="O37">
-        <v>18.19685054</v>
+        <v>18.181331984</v>
       </c>
       <c r="P37">
-        <v>42.45931792666667</v>
+        <v>42.42310796266666</v>
       </c>
       <c r="Q37">
-        <v>58.15931792666667</v>
+        <v>58.12310796266667</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2036479749573488</v>
+        <v>0.2055769830311991</v>
       </c>
       <c r="T37">
-        <v>1.100585937788906</v>
+        <v>1.114035835771662</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>34.50247377581854</v>
+        <v>33.54407172649024</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1442448691399675</v>
+        <v>0.1437950545576581</v>
       </c>
       <c r="C38">
-        <v>72.58408583801483</v>
+        <v>71.75264869804982</v>
       </c>
       <c r="D38">
-        <v>88.50648583801484</v>
+        <v>88.70344869804984</v>
       </c>
       <c r="E38">
-        <v>31.3824</v>
+        <v>32.4108</v>
       </c>
       <c r="F38">
-        <v>37.0224</v>
+        <v>38.0508</v>
       </c>
       <c r="G38">
         <v>21.1</v>
@@ -4403,28 +4403,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M38">
-        <v>1.86222672</v>
+        <v>1.91395524</v>
       </c>
       <c r="N38">
-        <v>60.60443994666667</v>
+        <v>60.55271142666667</v>
       </c>
       <c r="O38">
-        <v>18.181331984</v>
+        <v>18.165813428</v>
       </c>
       <c r="P38">
-        <v>42.42310796266666</v>
+        <v>42.38689799866667</v>
       </c>
       <c r="Q38">
-        <v>58.12310796266667</v>
+        <v>58.08689799866667</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2055769830311991</v>
+        <v>0.2075672294566002</v>
       </c>
       <c r="T38">
-        <v>1.114035835771662</v>
+        <v>1.127912714642759</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>33.54407172649025</v>
+        <v>32.63747519334186</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1437950545576581</v>
+        <v>0.1433452399753488</v>
       </c>
       <c r="C39">
-        <v>71.75264869804982</v>
+        <v>70.92209015796679</v>
       </c>
       <c r="D39">
-        <v>88.70344869804984</v>
+        <v>88.90129015796678</v>
       </c>
       <c r="E39">
-        <v>32.4108</v>
+        <v>33.4392</v>
       </c>
       <c r="F39">
-        <v>38.0508</v>
+        <v>39.0792</v>
       </c>
       <c r="G39">
         <v>21.1</v>
@@ -4485,28 +4485,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M39">
-        <v>1.91395524</v>
+        <v>1.96568376</v>
       </c>
       <c r="N39">
-        <v>60.55271142666667</v>
+        <v>60.50098290666667</v>
       </c>
       <c r="O39">
-        <v>18.165813428</v>
+        <v>18.150294872</v>
       </c>
       <c r="P39">
-        <v>42.38689799866667</v>
+        <v>42.35068803466667</v>
       </c>
       <c r="Q39">
-        <v>58.08689799866667</v>
+        <v>58.05068803466668</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2075672294566002</v>
+        <v>0.2096216773795949</v>
       </c>
       <c r="T39">
-        <v>1.127912714642759</v>
+        <v>1.142237234767762</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>32.63747519334186</v>
+        <v>31.77859426720129</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1433452399753488</v>
+        <v>0.1428954253930395</v>
       </c>
       <c r="C40">
-        <v>70.92209015796679</v>
+        <v>70.09241610971388</v>
       </c>
       <c r="D40">
-        <v>88.90129015796678</v>
+        <v>89.10001610971388</v>
       </c>
       <c r="E40">
-        <v>33.4392</v>
+        <v>34.4676</v>
       </c>
       <c r="F40">
-        <v>39.0792</v>
+        <v>40.10760000000001</v>
       </c>
       <c r="G40">
         <v>21.1</v>
@@ -4567,28 +4567,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M40">
-        <v>1.96568376</v>
+        <v>2.01741228</v>
       </c>
       <c r="N40">
-        <v>60.50098290666667</v>
+        <v>60.44925438666667</v>
       </c>
       <c r="O40">
-        <v>18.150294872</v>
+        <v>18.134776316</v>
       </c>
       <c r="P40">
-        <v>42.35068803466667</v>
+        <v>42.31447807066667</v>
       </c>
       <c r="Q40">
-        <v>58.05068803466668</v>
+        <v>58.01447807066667</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2096216773795949</v>
+        <v>0.2117434842508845</v>
       </c>
       <c r="T40">
-        <v>1.142237234767762</v>
+        <v>1.157031411290306</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>31.77859426720129</v>
+        <v>30.96375851676022</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1428954253930395</v>
+        <v>0.1424456108107302</v>
       </c>
       <c r="C41">
-        <v>70.09241610971388</v>
+        <v>69.26363249803973</v>
       </c>
       <c r="D41">
-        <v>89.10001610971388</v>
+        <v>89.29963249803973</v>
       </c>
       <c r="E41">
-        <v>34.4676</v>
+        <v>35.496</v>
       </c>
       <c r="F41">
-        <v>40.10760000000001</v>
+        <v>41.136</v>
       </c>
       <c r="G41">
         <v>21.1</v>
@@ -4649,28 +4649,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M41">
-        <v>2.01741228</v>
+        <v>2.0691408</v>
       </c>
       <c r="N41">
-        <v>60.44925438666667</v>
+        <v>60.39752586666667</v>
       </c>
       <c r="O41">
-        <v>18.134776316</v>
+        <v>18.11925776</v>
       </c>
       <c r="P41">
-        <v>42.31447807066667</v>
+        <v>42.27826810666667</v>
       </c>
       <c r="Q41">
-        <v>58.01447807066667</v>
+        <v>57.97826810666668</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2117434842508845</v>
+        <v>0.2139360180178837</v>
       </c>
       <c r="T41">
-        <v>1.157031411290306</v>
+        <v>1.172318727030269</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>30.96375851676022</v>
+        <v>30.18966455384122</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1424456108107302</v>
+        <v>0.1419957962284209</v>
       </c>
       <c r="C42">
-        <v>69.26363249803973</v>
+        <v>68.43574532108605</v>
       </c>
       <c r="D42">
-        <v>89.29963249803973</v>
+        <v>89.50014532108604</v>
       </c>
       <c r="E42">
-        <v>35.496</v>
+        <v>36.52440000000001</v>
       </c>
       <c r="F42">
-        <v>41.136</v>
+        <v>42.16440000000001</v>
       </c>
       <c r="G42">
         <v>21.1</v>
@@ -4731,28 +4731,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M42">
-        <v>2.0691408</v>
+        <v>2.12086932</v>
       </c>
       <c r="N42">
-        <v>60.39752586666667</v>
+        <v>60.34579734666667</v>
       </c>
       <c r="O42">
-        <v>18.11925776</v>
+        <v>18.103739204</v>
       </c>
       <c r="P42">
-        <v>42.27826810666667</v>
+        <v>42.24205814266667</v>
       </c>
       <c r="Q42">
-        <v>57.97826810666668</v>
+        <v>57.94205814266667</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2139360180178837</v>
+        <v>0.2162028749634253</v>
       </c>
       <c r="T42">
-        <v>1.172318727030269</v>
+        <v>1.188124256863111</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>30.18966455384122</v>
+        <v>29.45333127204022</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1419957962284209</v>
+        <v>0.1415459816461116</v>
       </c>
       <c r="C43">
-        <v>68.43574532108605</v>
+        <v>67.60876063098863</v>
       </c>
       <c r="D43">
-        <v>89.50014532108604</v>
+        <v>89.70156063098864</v>
       </c>
       <c r="E43">
-        <v>36.52440000000001</v>
+        <v>37.5528</v>
       </c>
       <c r="F43">
-        <v>42.16440000000001</v>
+        <v>43.19280000000001</v>
       </c>
       <c r="G43">
         <v>21.1</v>
@@ -4813,28 +4813,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M43">
-        <v>2.12086932</v>
+        <v>2.17259784</v>
       </c>
       <c r="N43">
-        <v>60.34579734666667</v>
+        <v>60.29406882666667</v>
       </c>
       <c r="O43">
-        <v>18.103739204</v>
+        <v>18.088220648</v>
       </c>
       <c r="P43">
-        <v>42.24205814266667</v>
+        <v>42.20584817866667</v>
       </c>
       <c r="Q43">
-        <v>57.94205814266667</v>
+        <v>57.90584817866667</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2162028749634253</v>
+        <v>0.2185478993898476</v>
       </c>
       <c r="T43">
-        <v>1.188124256863111</v>
+        <v>1.204474804966052</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>29.45333127204022</v>
+        <v>28.75206147984878</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1415459816461116</v>
+        <v>0.1410961670638023</v>
       </c>
       <c r="C44">
-        <v>67.60876063098863</v>
+        <v>66.78268453448618</v>
       </c>
       <c r="D44">
-        <v>89.70156063098864</v>
+        <v>89.90388453448618</v>
       </c>
       <c r="E44">
-        <v>37.5528</v>
+        <v>38.5812</v>
       </c>
       <c r="F44">
-        <v>43.1928</v>
+        <v>44.2212</v>
       </c>
       <c r="G44">
         <v>21.1</v>
@@ -4895,28 +4895,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M44">
-        <v>2.17259784</v>
+        <v>2.22432636</v>
       </c>
       <c r="N44">
-        <v>60.29406882666667</v>
+        <v>60.24234030666667</v>
       </c>
       <c r="O44">
-        <v>18.088220648</v>
+        <v>18.072702092</v>
       </c>
       <c r="P44">
-        <v>42.20584817866667</v>
+        <v>42.16963821466667</v>
       </c>
       <c r="Q44">
-        <v>57.90584817866667</v>
+        <v>57.86963821466667</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2185478993898476</v>
+        <v>0.2209752053750917</v>
       </c>
       <c r="T44">
-        <v>1.204474804966052</v>
+        <v>1.221399056511201</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>28.75206147984878</v>
+        <v>28.08340888729416</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1410961670638023</v>
+        <v>0.140646352481493</v>
       </c>
       <c r="C45">
-        <v>66.78268453448618</v>
+        <v>65.95752319353748</v>
       </c>
       <c r="D45">
-        <v>89.90388453448618</v>
+        <v>90.10712319353749</v>
       </c>
       <c r="E45">
-        <v>38.5812</v>
+        <v>39.6096</v>
       </c>
       <c r="F45">
-        <v>44.2212</v>
+        <v>45.2496</v>
       </c>
       <c r="G45">
         <v>21.1</v>
@@ -4977,28 +4977,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M45">
-        <v>2.22432636</v>
+        <v>2.27605488</v>
       </c>
       <c r="N45">
-        <v>60.24234030666667</v>
+        <v>60.19061178666667</v>
       </c>
       <c r="O45">
-        <v>18.072702092</v>
+        <v>18.057183536</v>
       </c>
       <c r="P45">
-        <v>42.16963821466667</v>
+        <v>42.13342825066667</v>
       </c>
       <c r="Q45">
-        <v>57.86963821466667</v>
+        <v>57.83342825066667</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2209752053750917</v>
+        <v>0.2234892008598089</v>
       </c>
       <c r="T45">
-        <v>1.221399056511201</v>
+        <v>1.238927745611534</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>28.08340888729416</v>
+        <v>27.44514959440112</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.140646352481493</v>
+        <v>0.1401965378991837</v>
       </c>
       <c r="C46">
-        <v>65.95752319353748</v>
+        <v>65.13328282594701</v>
       </c>
       <c r="D46">
-        <v>90.10712319353749</v>
+        <v>90.311282825947</v>
       </c>
       <c r="E46">
-        <v>39.6096</v>
+        <v>40.63800000000001</v>
       </c>
       <c r="F46">
-        <v>45.2496</v>
+        <v>46.27800000000001</v>
       </c>
       <c r="G46">
         <v>21.1</v>
@@ -5059,28 +5059,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M46">
-        <v>2.27605488</v>
+        <v>2.3277834</v>
       </c>
       <c r="N46">
-        <v>60.19061178666667</v>
+        <v>60.13888326666667</v>
       </c>
       <c r="O46">
-        <v>18.057183536</v>
+        <v>18.04166498</v>
       </c>
       <c r="P46">
-        <v>42.13342825066667</v>
+        <v>42.09721828666667</v>
       </c>
       <c r="Q46">
-        <v>57.83342825066667</v>
+        <v>57.79721828666666</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2234892008598089</v>
+        <v>0.2260946143621521</v>
       </c>
       <c r="T46">
-        <v>1.238927745611534</v>
+        <v>1.257093841588243</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>27.44514959440112</v>
+        <v>26.83525738119219</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1401965378991837</v>
+        <v>0.1397467233168743</v>
       </c>
       <c r="C47">
-        <v>65.13328282594701</v>
+        <v>64.30996970599901</v>
       </c>
       <c r="D47">
-        <v>90.311282825947</v>
+        <v>90.516369705999</v>
       </c>
       <c r="E47">
-        <v>40.63800000000001</v>
+        <v>41.6664</v>
       </c>
       <c r="F47">
-        <v>46.27800000000001</v>
+        <v>47.3064</v>
       </c>
       <c r="G47">
         <v>21.1</v>
@@ -5141,28 +5141,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M47">
-        <v>2.3277834</v>
+        <v>2.37951192</v>
       </c>
       <c r="N47">
-        <v>60.13888326666667</v>
+        <v>60.08715474666667</v>
       </c>
       <c r="O47">
-        <v>18.04166498</v>
+        <v>18.026146424</v>
       </c>
       <c r="P47">
-        <v>42.09721828666667</v>
+        <v>42.06100832266667</v>
       </c>
       <c r="Q47">
-        <v>57.79721828666666</v>
+        <v>57.76100832266667</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2260946143621521</v>
+        <v>0.2287965246608784</v>
       </c>
       <c r="T47">
-        <v>1.257093841588243</v>
+        <v>1.275932755934459</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>26.83525738119219</v>
+        <v>26.2518822207315</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1397467233168743</v>
+        <v>0.1392969087345651</v>
       </c>
       <c r="C48">
-        <v>64.30996970599901</v>
+        <v>63.48759016510016</v>
       </c>
       <c r="D48">
-        <v>90.516369705999</v>
+        <v>90.72239016510017</v>
       </c>
       <c r="E48">
-        <v>41.6664</v>
+        <v>42.6948</v>
       </c>
       <c r="F48">
-        <v>47.3064</v>
+        <v>48.3348</v>
       </c>
       <c r="G48">
         <v>21.1</v>
@@ -5223,28 +5223,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M48">
-        <v>2.37951192</v>
+        <v>2.43124044</v>
       </c>
       <c r="N48">
-        <v>60.08715474666667</v>
+        <v>60.03542622666667</v>
       </c>
       <c r="O48">
-        <v>18.026146424</v>
+        <v>18.010627868</v>
       </c>
       <c r="P48">
-        <v>42.06100832266667</v>
+        <v>42.02479835866667</v>
       </c>
       <c r="Q48">
-        <v>57.76100832266667</v>
+        <v>57.72479835866667</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2287965246608784</v>
+        <v>0.231600393838802</v>
       </c>
       <c r="T48">
-        <v>1.275932755934459</v>
+        <v>1.295482572708835</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>26.2518822207315</v>
+        <v>25.69333153518402</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1392969087345651</v>
+        <v>0.1388470941522558</v>
       </c>
       <c r="C49">
-        <v>63.48759016510016</v>
+        <v>62.66615059243136</v>
       </c>
       <c r="D49">
-        <v>90.72239016510017</v>
+        <v>90.92935059243138</v>
       </c>
       <c r="E49">
-        <v>42.6948</v>
+        <v>43.72320000000001</v>
       </c>
       <c r="F49">
-        <v>48.3348</v>
+        <v>49.36320000000001</v>
       </c>
       <c r="G49">
         <v>21.1</v>
@@ -5305,28 +5305,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M49">
-        <v>2.43124044</v>
+        <v>2.48296896</v>
       </c>
       <c r="N49">
-        <v>60.03542622666667</v>
+        <v>59.98369770666667</v>
       </c>
       <c r="O49">
-        <v>18.010627868</v>
+        <v>17.995109312</v>
       </c>
       <c r="P49">
-        <v>42.02479835866667</v>
+        <v>41.98858839466666</v>
       </c>
       <c r="Q49">
-        <v>57.72479835866667</v>
+        <v>57.68858839466667</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.231600393838802</v>
+        <v>0.2345121041389534</v>
       </c>
       <c r="T49">
-        <v>1.295482572708835</v>
+        <v>1.315784305512994</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>25.69333153518402</v>
+        <v>25.15805379486768</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1388470941522558</v>
+        <v>0.1383972795699464</v>
       </c>
       <c r="C50">
-        <v>62.66615059243137</v>
+        <v>61.84565743560808</v>
       </c>
       <c r="D50">
-        <v>90.92935059243138</v>
+        <v>91.13725743560808</v>
       </c>
       <c r="E50">
-        <v>43.7232</v>
+        <v>44.7516</v>
       </c>
       <c r="F50">
-        <v>49.3632</v>
+        <v>50.3916</v>
       </c>
       <c r="G50">
         <v>21.1</v>
@@ -5387,28 +5387,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M50">
-        <v>2.48296896</v>
+        <v>2.53469748</v>
       </c>
       <c r="N50">
-        <v>59.98369770666667</v>
+        <v>59.93196918666667</v>
       </c>
       <c r="O50">
-        <v>17.995109312</v>
+        <v>17.979590756</v>
       </c>
       <c r="P50">
-        <v>41.98858839466666</v>
+        <v>41.95237843066667</v>
       </c>
       <c r="Q50">
-        <v>57.68858839466667</v>
+        <v>57.65237843066667</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2345121041389534</v>
+        <v>0.2375379991567577</v>
       </c>
       <c r="T50">
-        <v>1.315784305512994</v>
+        <v>1.33688218470163</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>25.15805379486768</v>
+        <v>24.64462412558467</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1383972795699464</v>
+        <v>0.1379474649876371</v>
       </c>
       <c r="C51">
-        <v>61.84565743560808</v>
+        <v>61.02611720134978</v>
       </c>
       <c r="D51">
-        <v>91.13725743560808</v>
+        <v>91.34611720134978</v>
       </c>
       <c r="E51">
-        <v>44.7516</v>
+        <v>45.78</v>
       </c>
       <c r="F51">
-        <v>50.3916</v>
+        <v>51.42</v>
       </c>
       <c r="G51">
         <v>21.1</v>
@@ -5469,28 +5469,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M51">
-        <v>2.53469748</v>
+        <v>2.586426</v>
       </c>
       <c r="N51">
-        <v>59.93196918666667</v>
+        <v>59.88024066666667</v>
       </c>
       <c r="O51">
-        <v>17.979590756</v>
+        <v>17.9640722</v>
       </c>
       <c r="P51">
-        <v>41.95237843066667</v>
+        <v>41.91616846666666</v>
       </c>
       <c r="Q51">
-        <v>57.65237843066667</v>
+        <v>57.61616846666666</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2375379991567577</v>
+        <v>0.2406849299752743</v>
       </c>
       <c r="T51">
-        <v>1.33688218470163</v>
+        <v>1.358823979057812</v>
       </c>
       <c r="U51">
         <v>0.0503</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>24.64462412558467</v>
+        <v>24.15173164307298</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1379474649876371</v>
+        <v>0.1374976504053279</v>
       </c>
       <c r="C52">
-        <v>61.02611720134978</v>
+        <v>60.20753645615897</v>
       </c>
       <c r="D52">
-        <v>91.34611720134978</v>
+        <v>91.55593645615897</v>
       </c>
       <c r="E52">
-        <v>45.78</v>
+        <v>46.8084</v>
       </c>
       <c r="F52">
-        <v>51.42</v>
+        <v>52.4484</v>
       </c>
       <c r="G52">
         <v>21.1</v>
@@ -5551,28 +5551,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M52">
-        <v>2.586426</v>
+        <v>2.63815452</v>
       </c>
       <c r="N52">
-        <v>59.88024066666667</v>
+        <v>59.82851214666667</v>
       </c>
       <c r="O52">
-        <v>17.9640722</v>
+        <v>17.948553644</v>
       </c>
       <c r="P52">
-        <v>41.91616846666666</v>
+        <v>41.87995850266667</v>
       </c>
       <c r="Q52">
-        <v>57.61616846666666</v>
+        <v>57.57995850266667</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2406849299752743</v>
+        <v>0.2439603069496487</v>
       </c>
       <c r="T52">
-        <v>1.358823979057812</v>
+        <v>1.381661356857103</v>
       </c>
       <c r="U52">
         <v>0.0503</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>24.15173164307298</v>
+        <v>23.67816827752253</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1374976504053279</v>
+        <v>0.1370478358230185</v>
       </c>
       <c r="C53">
-        <v>60.20753645615897</v>
+        <v>59.38992182700937</v>
       </c>
       <c r="D53">
-        <v>91.55593645615897</v>
+        <v>91.76672182700936</v>
       </c>
       <c r="E53">
-        <v>46.8084</v>
+        <v>47.8368</v>
       </c>
       <c r="F53">
-        <v>52.4484</v>
+        <v>53.4768</v>
       </c>
       <c r="G53">
         <v>21.1</v>
@@ -5633,28 +5633,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M53">
-        <v>2.63815452</v>
+        <v>2.68988304</v>
       </c>
       <c r="N53">
-        <v>59.82851214666667</v>
+        <v>59.77678362666667</v>
       </c>
       <c r="O53">
-        <v>17.948553644</v>
+        <v>17.933035088</v>
       </c>
       <c r="P53">
-        <v>41.87995850266667</v>
+        <v>41.84374853866667</v>
       </c>
       <c r="Q53">
-        <v>57.57995850266667</v>
+        <v>57.54374853866668</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2439603069496487</v>
+        <v>0.2473721579646219</v>
       </c>
       <c r="T53">
-        <v>1.381661356857103</v>
+        <v>1.405450292064697</v>
       </c>
       <c r="U53">
         <v>0.0503</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>23.67816827752253</v>
+        <v>23.22281888757017</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1370478358230185</v>
+        <v>0.1365980212407092</v>
       </c>
       <c r="C54">
-        <v>59.38992182700937</v>
+        <v>58.57328000204336</v>
       </c>
       <c r="D54">
-        <v>91.76672182700936</v>
+        <v>91.97848000204337</v>
       </c>
       <c r="E54">
-        <v>47.8368</v>
+        <v>48.8652</v>
       </c>
       <c r="F54">
-        <v>53.4768</v>
+        <v>54.5052</v>
       </c>
       <c r="G54">
         <v>21.1</v>
@@ -5715,28 +5715,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M54">
-        <v>2.68988304</v>
+        <v>2.74161156</v>
       </c>
       <c r="N54">
-        <v>59.77678362666667</v>
+        <v>59.72505510666667</v>
       </c>
       <c r="O54">
-        <v>17.933035088</v>
+        <v>17.917516532</v>
       </c>
       <c r="P54">
-        <v>41.84374853866667</v>
+        <v>41.80753857466667</v>
       </c>
       <c r="Q54">
-        <v>57.54374853866668</v>
+        <v>57.50753857466667</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2473721579646219</v>
+        <v>0.2509291941291685</v>
       </c>
       <c r="T54">
-        <v>1.405450292064697</v>
+        <v>1.430251522387509</v>
       </c>
       <c r="U54">
         <v>0.0503</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>23.22281888757017</v>
+        <v>22.78465249346507</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1365980212407092</v>
+        <v>0.1361482066583999</v>
       </c>
       <c r="C55">
-        <v>58.57328000204336</v>
+        <v>57.75761773127965</v>
       </c>
       <c r="D55">
-        <v>91.97848000204337</v>
+        <v>92.19121773127965</v>
       </c>
       <c r="E55">
-        <v>48.8652</v>
+        <v>49.89360000000001</v>
       </c>
       <c r="F55">
-        <v>54.5052</v>
+        <v>55.53360000000001</v>
       </c>
       <c r="G55">
         <v>21.1</v>
@@ -5797,28 +5797,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M55">
-        <v>2.74161156</v>
+        <v>2.79334008</v>
       </c>
       <c r="N55">
-        <v>59.72505510666667</v>
+        <v>59.67332658666667</v>
       </c>
       <c r="O55">
-        <v>17.917516532</v>
+        <v>17.901997976</v>
       </c>
       <c r="P55">
-        <v>41.80753857466667</v>
+        <v>41.77132861066667</v>
       </c>
       <c r="Q55">
-        <v>57.50753857466667</v>
+        <v>57.47132861066667</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2509291941291685</v>
+        <v>0.2546408840399998</v>
       </c>
       <c r="T55">
-        <v>1.430251522387509</v>
+        <v>1.456131067072182</v>
       </c>
       <c r="U55">
         <v>0.0503</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>22.78465249346507</v>
+        <v>22.36271448432683</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1361482066583999</v>
+        <v>0.1356983920760906</v>
       </c>
       <c r="C56">
-        <v>57.75761773127965</v>
+        <v>56.94294182733038</v>
       </c>
       <c r="D56">
-        <v>92.19121773127965</v>
+        <v>92.40494182733039</v>
       </c>
       <c r="E56">
-        <v>49.89360000000001</v>
+        <v>50.922</v>
       </c>
       <c r="F56">
-        <v>55.53360000000001</v>
+        <v>56.562</v>
       </c>
       <c r="G56">
         <v>21.1</v>
@@ -5879,28 +5879,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M56">
-        <v>2.79334008</v>
+        <v>2.8450686</v>
       </c>
       <c r="N56">
-        <v>59.67332658666667</v>
+        <v>59.62159806666667</v>
       </c>
       <c r="O56">
-        <v>17.901997976</v>
+        <v>17.88647942</v>
       </c>
       <c r="P56">
-        <v>41.77132861066667</v>
+        <v>41.73511864666667</v>
       </c>
       <c r="Q56">
-        <v>57.47132861066667</v>
+        <v>57.43511864666667</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2546408840399998</v>
+        <v>0.258517537946868</v>
       </c>
       <c r="T56">
-        <v>1.456131067072182</v>
+        <v>1.48316081374284</v>
       </c>
       <c r="U56">
         <v>0.0503</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>22.36271448432683</v>
+        <v>21.95611967552089</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1356983920760906</v>
+        <v>0.1352485774937813</v>
       </c>
       <c r="C57">
-        <v>56.94294182733038</v>
+        <v>56.12925916612839</v>
       </c>
       <c r="D57">
-        <v>92.40494182733039</v>
+        <v>92.6196591661284</v>
       </c>
       <c r="E57">
-        <v>50.922</v>
+        <v>51.95040000000001</v>
       </c>
       <c r="F57">
-        <v>56.562</v>
+        <v>57.59040000000001</v>
       </c>
       <c r="G57">
         <v>21.1</v>
@@ -5961,28 +5961,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M57">
-        <v>2.8450686</v>
+        <v>2.89679712</v>
       </c>
       <c r="N57">
-        <v>59.62159806666667</v>
+        <v>59.56986954666667</v>
       </c>
       <c r="O57">
-        <v>17.88647942</v>
+        <v>17.870960864</v>
       </c>
       <c r="P57">
-        <v>41.73511864666667</v>
+        <v>41.69890868266667</v>
       </c>
       <c r="Q57">
-        <v>57.43511864666667</v>
+        <v>57.39890868266667</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.258517537946868</v>
+        <v>0.2625704033949575</v>
       </c>
       <c r="T57">
-        <v>1.48316081374284</v>
+        <v>1.511419185262165</v>
       </c>
       <c r="U57">
         <v>0.0503</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>21.95611967552089</v>
+        <v>21.56404610988658</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1352485774937813</v>
+        <v>0.134798762911472</v>
       </c>
       <c r="C58">
-        <v>56.12925916612839</v>
+        <v>55.31657668766461</v>
       </c>
       <c r="D58">
-        <v>92.6196591661284</v>
+        <v>92.83537668766461</v>
       </c>
       <c r="E58">
-        <v>51.95040000000001</v>
+        <v>52.97880000000001</v>
       </c>
       <c r="F58">
-        <v>57.59040000000001</v>
+        <v>58.61880000000001</v>
       </c>
       <c r="G58">
         <v>21.1</v>
@@ -6043,28 +6043,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M58">
-        <v>2.89679712</v>
+        <v>2.94852564</v>
       </c>
       <c r="N58">
-        <v>59.56986954666667</v>
+        <v>59.51814102666667</v>
       </c>
       <c r="O58">
-        <v>17.870960864</v>
+        <v>17.855442308</v>
       </c>
       <c r="P58">
-        <v>41.69890868266667</v>
+        <v>41.66269871866667</v>
       </c>
       <c r="Q58">
-        <v>57.39890868266667</v>
+        <v>57.36269871866666</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2625704033949575</v>
+        <v>0.2668117742127256</v>
       </c>
       <c r="T58">
-        <v>1.511419185262165</v>
+        <v>1.540991899642854</v>
       </c>
       <c r="U58">
         <v>0.0503</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>21.56404610988658</v>
+        <v>21.18572951146752</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.134798762911472</v>
+        <v>0.1343489483291627</v>
       </c>
       <c r="C59">
-        <v>55.31657668766461</v>
+        <v>54.50490139673563</v>
       </c>
       <c r="D59">
-        <v>92.83537668766461</v>
+        <v>93.05210139673564</v>
       </c>
       <c r="E59">
-        <v>52.97880000000001</v>
+        <v>54.00720000000001</v>
       </c>
       <c r="F59">
-        <v>58.61880000000001</v>
+        <v>59.64720000000001</v>
       </c>
       <c r="G59">
         <v>21.1</v>
@@ -6125,28 +6125,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M59">
-        <v>2.94852564</v>
+        <v>3.00025416</v>
       </c>
       <c r="N59">
-        <v>59.51814102666667</v>
+        <v>59.46641250666667</v>
       </c>
       <c r="O59">
-        <v>17.855442308</v>
+        <v>17.839923752</v>
       </c>
       <c r="P59">
-        <v>41.66269871866667</v>
+        <v>41.62648875466667</v>
       </c>
       <c r="Q59">
-        <v>57.36269871866666</v>
+        <v>57.32648875466667</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2668117742127256</v>
+        <v>0.2712551150694349</v>
       </c>
       <c r="T59">
-        <v>1.540991899642854</v>
+        <v>1.571972838517861</v>
       </c>
       <c r="U59">
         <v>0.0503</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>21.18572951146752</v>
+        <v>20.82045831299395</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1343489483291627</v>
+        <v>0.1338991337468534</v>
       </c>
       <c r="C60">
-        <v>54.50490139673562</v>
+        <v>53.69424036370223</v>
       </c>
       <c r="D60">
-        <v>93.05210139673561</v>
+        <v>93.26984036370222</v>
       </c>
       <c r="E60">
-        <v>54.0072</v>
+        <v>55.0356</v>
       </c>
       <c r="F60">
-        <v>59.6472</v>
+        <v>60.6756</v>
       </c>
       <c r="G60">
         <v>21.1</v>
@@ -6207,28 +6207,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M60">
-        <v>3.00025416</v>
+        <v>3.05198268</v>
       </c>
       <c r="N60">
-        <v>59.46641250666667</v>
+        <v>59.41468398666667</v>
       </c>
       <c r="O60">
-        <v>17.839923752</v>
+        <v>17.824405196</v>
       </c>
       <c r="P60">
-        <v>41.62648875466667</v>
+        <v>41.59027879066667</v>
       </c>
       <c r="Q60">
-        <v>57.32648875466667</v>
+        <v>57.29027879066666</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2712551150694349</v>
+        <v>0.2759152042606179</v>
       </c>
       <c r="T60">
-        <v>1.57197283851786</v>
+        <v>1.604465042703843</v>
       </c>
       <c r="U60">
         <v>0.0503</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>20.82045831299395</v>
+        <v>20.4675691890449</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1338991337468534</v>
+        <v>0.1334493191645441</v>
       </c>
       <c r="C61">
-        <v>53.69424036370223</v>
+        <v>52.88460072525792</v>
       </c>
       <c r="D61">
-        <v>93.26984036370222</v>
+        <v>93.48860072525791</v>
       </c>
       <c r="E61">
-        <v>55.0356</v>
+        <v>56.064</v>
       </c>
       <c r="F61">
-        <v>60.6756</v>
+        <v>61.704</v>
       </c>
       <c r="G61">
         <v>21.1</v>
@@ -6289,28 +6289,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M61">
-        <v>3.05198268</v>
+        <v>3.1037112</v>
       </c>
       <c r="N61">
-        <v>59.41468398666667</v>
+        <v>59.36295546666667</v>
       </c>
       <c r="O61">
-        <v>17.824405196</v>
+        <v>17.80888664</v>
       </c>
       <c r="P61">
-        <v>41.59027879066667</v>
+        <v>41.55406882666666</v>
       </c>
       <c r="Q61">
-        <v>57.29027879066666</v>
+        <v>57.25406882666667</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2759152042606179</v>
+        <v>0.2808082979113601</v>
       </c>
       <c r="T61">
-        <v>1.604465042703843</v>
+        <v>1.638581857099126</v>
       </c>
       <c r="U61">
         <v>0.0503</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>20.4675691890449</v>
+        <v>20.12644303589415</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1334493191645441</v>
+        <v>0.1329995045822348</v>
       </c>
       <c r="C62">
-        <v>52.88460072525792</v>
+        <v>52.07598968520897</v>
       </c>
       <c r="D62">
-        <v>93.48860072525791</v>
+        <v>93.70838968520896</v>
       </c>
       <c r="E62">
-        <v>56.064</v>
+        <v>57.0924</v>
       </c>
       <c r="F62">
-        <v>61.704</v>
+        <v>62.7324</v>
       </c>
       <c r="G62">
         <v>21.1</v>
@@ -6371,28 +6371,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M62">
-        <v>3.1037112</v>
+        <v>3.15543972</v>
       </c>
       <c r="N62">
-        <v>59.36295546666667</v>
+        <v>59.31122694666667</v>
       </c>
       <c r="O62">
-        <v>17.80888664</v>
+        <v>17.793368084</v>
       </c>
       <c r="P62">
-        <v>41.55406882666666</v>
+        <v>41.51785886266667</v>
       </c>
       <c r="Q62">
-        <v>57.25406882666667</v>
+        <v>57.21785886266667</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2808082979113601</v>
+        <v>0.2859523194416275</v>
       </c>
       <c r="T62">
-        <v>1.638581857099126</v>
+        <v>1.674448251719807</v>
       </c>
       <c r="U62">
         <v>0.0503</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>20.12644303589415</v>
+        <v>19.79650134678113</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1329995045822348</v>
+        <v>0.1325496899999254</v>
       </c>
       <c r="C63">
-        <v>52.07598968520897</v>
+        <v>51.26841451526498</v>
       </c>
       <c r="D63">
-        <v>93.70838968520896</v>
+        <v>93.92921451526499</v>
       </c>
       <c r="E63">
-        <v>57.0924</v>
+        <v>58.1208</v>
       </c>
       <c r="F63">
-        <v>62.7324</v>
+        <v>63.7608</v>
       </c>
       <c r="G63">
         <v>21.1</v>
@@ -6453,28 +6453,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M63">
-        <v>3.15543972</v>
+        <v>3.20716824</v>
       </c>
       <c r="N63">
-        <v>59.31122694666667</v>
+        <v>59.25949842666667</v>
       </c>
       <c r="O63">
-        <v>17.793368084</v>
+        <v>17.777849528</v>
       </c>
       <c r="P63">
-        <v>41.51785886266667</v>
+        <v>41.48164889866666</v>
       </c>
       <c r="Q63">
-        <v>57.21785886266667</v>
+        <v>57.18164889866667</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2859523194416275</v>
+        <v>0.2913670789471722</v>
       </c>
       <c r="T63">
-        <v>1.674448251719807</v>
+        <v>1.712202351320524</v>
       </c>
       <c r="U63">
         <v>0.0503</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>19.79650134678113</v>
+        <v>19.47720293796208</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1325496899999254</v>
+        <v>0.1320998754176161</v>
       </c>
       <c r="C64">
-        <v>51.26841451526498</v>
+        <v>50.46188255584092</v>
       </c>
       <c r="D64">
-        <v>93.92921451526499</v>
+        <v>94.15108255584092</v>
       </c>
       <c r="E64">
-        <v>58.1208</v>
+        <v>59.14920000000001</v>
       </c>
       <c r="F64">
-        <v>63.7608</v>
+        <v>64.78920000000001</v>
       </c>
       <c r="G64">
         <v>21.1</v>
@@ -6535,28 +6535,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M64">
-        <v>3.20716824</v>
+        <v>3.25889676</v>
       </c>
       <c r="N64">
-        <v>59.25949842666667</v>
+        <v>59.20776990666667</v>
       </c>
       <c r="O64">
-        <v>17.777849528</v>
+        <v>17.762330972</v>
       </c>
       <c r="P64">
-        <v>41.48164889866666</v>
+        <v>41.44543893466667</v>
       </c>
       <c r="Q64">
-        <v>57.18164889866667</v>
+        <v>57.14543893466667</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2913670789471722</v>
+        <v>0.2970745281557193</v>
       </c>
       <c r="T64">
-        <v>1.712202351320524</v>
+        <v>1.751997213061821</v>
       </c>
       <c r="U64">
         <v>0.0503</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>19.47720293796208</v>
+        <v>19.16804098656585</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1320998754176161</v>
+        <v>0.1316500608353068</v>
       </c>
       <c r="C65">
-        <v>50.46188255584092</v>
+        <v>49.65640121687045</v>
       </c>
       <c r="D65">
-        <v>94.15108255584092</v>
+        <v>94.37400121687045</v>
       </c>
       <c r="E65">
-        <v>59.14920000000001</v>
+        <v>60.1776</v>
       </c>
       <c r="F65">
-        <v>64.78920000000001</v>
+        <v>65.8176</v>
       </c>
       <c r="G65">
         <v>21.1</v>
@@ -6617,28 +6617,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M65">
-        <v>3.25889676</v>
+        <v>3.31062528</v>
       </c>
       <c r="N65">
-        <v>59.20776990666667</v>
+        <v>59.15604138666667</v>
       </c>
       <c r="O65">
-        <v>17.762330972</v>
+        <v>17.746812416</v>
       </c>
       <c r="P65">
-        <v>41.44543893466667</v>
+        <v>41.40922897066667</v>
       </c>
       <c r="Q65">
-        <v>57.14543893466667</v>
+        <v>57.10922897066668</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2970745281557193</v>
+        <v>0.3030990578758523</v>
       </c>
       <c r="T65">
-        <v>1.751997213061821</v>
+        <v>1.794002900455411</v>
       </c>
       <c r="U65">
         <v>0.0503</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>19.16804098656585</v>
+        <v>18.86854034615077</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1316500608353068</v>
+        <v>0.1312002462529975</v>
       </c>
       <c r="C66">
-        <v>49.65640121687045</v>
+        <v>48.85197797863088</v>
       </c>
       <c r="D66">
-        <v>94.37400121687045</v>
+        <v>94.59797797863089</v>
       </c>
       <c r="E66">
-        <v>60.1776</v>
+        <v>61.206</v>
       </c>
       <c r="F66">
-        <v>65.8176</v>
+        <v>66.846</v>
       </c>
       <c r="G66">
         <v>21.1</v>
@@ -6699,28 +6699,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M66">
-        <v>3.31062528</v>
+        <v>3.3623538</v>
       </c>
       <c r="N66">
-        <v>59.15604138666667</v>
+        <v>59.10431286666667</v>
       </c>
       <c r="O66">
-        <v>17.746812416</v>
+        <v>17.73129386</v>
       </c>
       <c r="P66">
-        <v>41.40922897066667</v>
+        <v>41.37301900666667</v>
       </c>
       <c r="Q66">
-        <v>57.10922897066668</v>
+        <v>57.07301900666667</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3030990578758523</v>
+        <v>0.3094678464371358</v>
       </c>
       <c r="T66">
-        <v>1.794002900455411</v>
+        <v>1.838408912842922</v>
       </c>
       <c r="U66">
         <v>0.0503</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>18.86854034615077</v>
+        <v>18.57825511005613</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1312002462529975</v>
+        <v>0.1307504316706882</v>
       </c>
       <c r="C67">
-        <v>48.85197797863088</v>
+        <v>48.04862039257995</v>
       </c>
       <c r="D67">
-        <v>94.59797797863089</v>
+        <v>94.82302039257995</v>
       </c>
       <c r="E67">
-        <v>61.206</v>
+        <v>62.23440000000001</v>
       </c>
       <c r="F67">
-        <v>66.846</v>
+        <v>67.87440000000001</v>
       </c>
       <c r="G67">
         <v>21.1</v>
@@ -6781,28 +6781,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M67">
-        <v>3.3623538</v>
+        <v>3.41408232</v>
       </c>
       <c r="N67">
-        <v>59.10431286666667</v>
+        <v>59.05258434666667</v>
       </c>
       <c r="O67">
-        <v>17.73129386</v>
+        <v>17.715775304</v>
       </c>
       <c r="P67">
-        <v>41.37301900666667</v>
+        <v>41.33680904266667</v>
       </c>
       <c r="Q67">
-        <v>57.07301900666667</v>
+        <v>57.03680904266668</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3094678464371358</v>
+        <v>0.3162112696196712</v>
       </c>
       <c r="T67">
-        <v>1.838408912842922</v>
+        <v>1.885427043606168</v>
       </c>
       <c r="U67">
         <v>0.0503</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>18.57825511005613</v>
+        <v>18.2967663962674</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1307504316706882</v>
+        <v>0.1303006170883789</v>
       </c>
       <c r="C68">
-        <v>48.04862039257995</v>
+        <v>47.24633608220432</v>
       </c>
       <c r="D68">
-        <v>94.82302039257995</v>
+        <v>95.04913608220433</v>
       </c>
       <c r="E68">
-        <v>62.23440000000001</v>
+        <v>63.26280000000001</v>
       </c>
       <c r="F68">
-        <v>67.87440000000001</v>
+        <v>68.90280000000001</v>
       </c>
       <c r="G68">
         <v>21.1</v>
@@ -6863,28 +6863,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M68">
-        <v>3.41408232</v>
+        <v>3.465810840000001</v>
       </c>
       <c r="N68">
-        <v>59.05258434666667</v>
+        <v>59.00085582666667</v>
       </c>
       <c r="O68">
-        <v>17.715775304</v>
+        <v>17.700256748</v>
       </c>
       <c r="P68">
-        <v>41.33680904266667</v>
+        <v>41.30059907866666</v>
       </c>
       <c r="Q68">
-        <v>57.03680904266668</v>
+        <v>57.00059907866667</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3162112696196712</v>
+        <v>0.3233633851162998</v>
       </c>
       <c r="T68">
-        <v>1.885427043606168</v>
+        <v>1.935294758052035</v>
       </c>
       <c r="U68">
         <v>0.0503</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>18.2967663962674</v>
+        <v>18.02368033065147</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1303006170883789</v>
+        <v>0.1298508025060696</v>
       </c>
       <c r="C69">
-        <v>47.24633608220432</v>
+        <v>46.44513274388071</v>
       </c>
       <c r="D69">
-        <v>95.04913608220433</v>
+        <v>95.2763327438807</v>
       </c>
       <c r="E69">
-        <v>63.26280000000001</v>
+        <v>64.2912</v>
       </c>
       <c r="F69">
-        <v>68.90280000000001</v>
+        <v>69.9312</v>
       </c>
       <c r="G69">
         <v>21.1</v>
@@ -6945,28 +6945,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M69">
-        <v>3.465810840000001</v>
+        <v>3.51753936</v>
       </c>
       <c r="N69">
-        <v>59.00085582666667</v>
+        <v>58.94912730666667</v>
       </c>
       <c r="O69">
-        <v>17.700256748</v>
+        <v>17.684738192</v>
       </c>
       <c r="P69">
-        <v>41.30059907866666</v>
+        <v>41.26438911466667</v>
       </c>
       <c r="Q69">
-        <v>57.00059907866667</v>
+        <v>56.96438911466667</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3233633851162998</v>
+        <v>0.3309625078314675</v>
       </c>
       <c r="T69">
-        <v>1.935294758052035</v>
+        <v>1.988279204650769</v>
       </c>
       <c r="U69">
         <v>0.0503</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>18.02368033065147</v>
+        <v>17.75862620814189</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1298508025060696</v>
+        <v>0.1294009879237603</v>
       </c>
       <c r="C70">
-        <v>46.44513274388071</v>
+        <v>45.64501814774884</v>
       </c>
       <c r="D70">
-        <v>95.2763327438807</v>
+        <v>95.50461814774886</v>
       </c>
       <c r="E70">
-        <v>64.2912</v>
+        <v>65.31960000000001</v>
       </c>
       <c r="F70">
-        <v>69.9312</v>
+        <v>70.95960000000001</v>
       </c>
       <c r="G70">
         <v>21.1</v>
@@ -7027,28 +7027,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M70">
-        <v>3.51753936</v>
+        <v>3.56926788</v>
       </c>
       <c r="N70">
-        <v>58.94912730666667</v>
+        <v>58.89739878666667</v>
       </c>
       <c r="O70">
-        <v>17.684738192</v>
+        <v>17.669219636</v>
       </c>
       <c r="P70">
-        <v>41.26438911466667</v>
+        <v>41.22817915066667</v>
       </c>
       <c r="Q70">
-        <v>56.96438911466667</v>
+        <v>56.92817915066667</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3309625078314675</v>
+        <v>0.3390518965282591</v>
       </c>
       <c r="T70">
-        <v>1.988279204650769</v>
+        <v>2.044682002642969</v>
       </c>
       <c r="U70">
         <v>0.0503</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>17.75862620814189</v>
+        <v>17.501254813821</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1294009879237603</v>
+        <v>0.128951173341451</v>
       </c>
       <c r="C71">
-        <v>45.64501814774884</v>
+        <v>44.84600013859752</v>
       </c>
       <c r="D71">
-        <v>95.50461814774886</v>
+        <v>95.73400013859752</v>
       </c>
       <c r="E71">
-        <v>65.31960000000001</v>
+        <v>66.34800000000001</v>
       </c>
       <c r="F71">
-        <v>70.95960000000001</v>
+        <v>71.98800000000001</v>
       </c>
       <c r="G71">
         <v>21.1</v>
@@ -7109,28 +7109,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M71">
-        <v>3.56926788</v>
+        <v>3.620996400000001</v>
       </c>
       <c r="N71">
-        <v>58.89739878666667</v>
+        <v>58.84567026666667</v>
       </c>
       <c r="O71">
-        <v>17.669219636</v>
+        <v>17.65370108</v>
       </c>
       <c r="P71">
-        <v>41.22817915066667</v>
+        <v>41.19196918666667</v>
       </c>
       <c r="Q71">
-        <v>56.92817915066667</v>
+        <v>56.89196918666667</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3390518965282591</v>
+        <v>0.3476805778048367</v>
       </c>
       <c r="T71">
-        <v>2.044682002642969</v>
+        <v>2.104844987167983</v>
       </c>
       <c r="U71">
         <v>0.0503</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>17.501254813821</v>
+        <v>17.25123688790926</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.128951173341451</v>
+        <v>0.1285013587591417</v>
       </c>
       <c r="C72">
-        <v>44.84600013859752</v>
+        <v>44.04808663676309</v>
       </c>
       <c r="D72">
-        <v>95.73400013859752</v>
+        <v>95.9644866367631</v>
       </c>
       <c r="E72">
-        <v>66.34800000000001</v>
+        <v>67.3764</v>
       </c>
       <c r="F72">
-        <v>71.98800000000001</v>
+        <v>73.0164</v>
       </c>
       <c r="G72">
         <v>21.1</v>
@@ -7191,28 +7191,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M72">
-        <v>3.620996400000001</v>
+        <v>3.67272492</v>
       </c>
       <c r="N72">
-        <v>58.84567026666667</v>
+        <v>58.79394174666667</v>
       </c>
       <c r="O72">
-        <v>17.65370108</v>
+        <v>17.638182524</v>
       </c>
       <c r="P72">
-        <v>41.19196918666667</v>
+        <v>41.15575922266667</v>
       </c>
       <c r="Q72">
-        <v>56.89196918666667</v>
+        <v>56.85575922266666</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3476805778048367</v>
+        <v>0.3569043405487645</v>
       </c>
       <c r="T72">
-        <v>2.104844987167983</v>
+        <v>2.16915714303955</v>
       </c>
       <c r="U72">
         <v>0.0503</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>17.25123688790926</v>
+        <v>17.00826172047393</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1285013587591417</v>
+        <v>0.1280515441768324</v>
       </c>
       <c r="C73">
-        <v>44.04808663676309</v>
+        <v>43.25128563904106</v>
       </c>
       <c r="D73">
-        <v>95.9644866367631</v>
+        <v>96.19608563904104</v>
       </c>
       <c r="E73">
-        <v>67.3764</v>
+        <v>68.40479999999999</v>
       </c>
       <c r="F73">
-        <v>73.0164</v>
+        <v>74.0448</v>
       </c>
       <c r="G73">
         <v>21.1</v>
@@ -7273,28 +7273,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M73">
-        <v>3.67272492</v>
+        <v>3.72445344</v>
       </c>
       <c r="N73">
-        <v>58.79394174666667</v>
+        <v>58.74221322666667</v>
       </c>
       <c r="O73">
-        <v>17.638182524</v>
+        <v>17.622663968</v>
       </c>
       <c r="P73">
-        <v>41.15575922266667</v>
+        <v>41.11954925866667</v>
       </c>
       <c r="Q73">
-        <v>56.85575922266666</v>
+        <v>56.81954925866667</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3569043405487644</v>
+        <v>0.366786943488687</v>
       </c>
       <c r="T73">
-        <v>2.169157143039549</v>
+        <v>2.238063024330513</v>
       </c>
       <c r="U73">
         <v>0.0503</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>17.00826172047393</v>
+        <v>16.77203586324513</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1280515441768324</v>
+        <v>0.1276017295945231</v>
       </c>
       <c r="C74">
-        <v>43.25128563904106</v>
+        <v>42.45560521961097</v>
       </c>
       <c r="D74">
-        <v>96.19608563904104</v>
+        <v>96.42880521961098</v>
       </c>
       <c r="E74">
-        <v>68.40479999999999</v>
+        <v>69.4332</v>
       </c>
       <c r="F74">
-        <v>74.0448</v>
+        <v>75.0732</v>
       </c>
       <c r="G74">
         <v>21.1</v>
@@ -7355,28 +7355,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M74">
-        <v>3.72445344</v>
+        <v>3.77618196</v>
       </c>
       <c r="N74">
-        <v>58.74221322666667</v>
+        <v>58.69048470666667</v>
       </c>
       <c r="O74">
-        <v>17.622663968</v>
+        <v>17.607145412</v>
       </c>
       <c r="P74">
-        <v>41.11954925866667</v>
+        <v>41.08333929466667</v>
       </c>
       <c r="Q74">
-        <v>56.81954925866667</v>
+        <v>56.78333929466667</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.366786943488687</v>
+        <v>0.3774015910908262</v>
       </c>
       <c r="T74">
-        <v>2.238063024330513</v>
+        <v>2.312073044976363</v>
       </c>
       <c r="U74">
         <v>0.0503</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>16.77203586324513</v>
+        <v>16.54228194731026</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1276017295945231</v>
+        <v>0.1271519150122138</v>
       </c>
       <c r="C75">
-        <v>42.45560521961097</v>
+        <v>41.66105353097488</v>
       </c>
       <c r="D75">
-        <v>96.42880521961098</v>
+        <v>96.66265353097488</v>
       </c>
       <c r="E75">
-        <v>69.4332</v>
+        <v>70.4616</v>
       </c>
       <c r="F75">
-        <v>75.0732</v>
+        <v>76.1016</v>
       </c>
       <c r="G75">
         <v>21.1</v>
@@ -7437,28 +7437,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M75">
-        <v>3.77618196</v>
+        <v>3.82791048</v>
       </c>
       <c r="N75">
-        <v>58.69048470666667</v>
+        <v>58.63875618666667</v>
       </c>
       <c r="O75">
-        <v>17.607145412</v>
+        <v>17.591626856</v>
       </c>
       <c r="P75">
-        <v>41.08333929466667</v>
+        <v>41.04712933066666</v>
       </c>
       <c r="Q75">
-        <v>56.78333929466667</v>
+        <v>56.74712933066667</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3774015910908262</v>
+        <v>0.388832750046976</v>
       </c>
       <c r="T75">
-        <v>2.312073044976363</v>
+        <v>2.391776144133433</v>
       </c>
       <c r="U75">
         <v>0.0503</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>16.54228194731026</v>
+        <v>16.31873759667093</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1271519150122138</v>
+        <v>0.1267021004299044</v>
       </c>
       <c r="C76">
-        <v>41.66105353097488</v>
+        <v>40.86763880490909</v>
       </c>
       <c r="D76">
-        <v>96.66265353097488</v>
+        <v>96.89763880490908</v>
       </c>
       <c r="E76">
-        <v>70.4616</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="F76">
-        <v>76.1016</v>
+        <v>77.13</v>
       </c>
       <c r="G76">
         <v>21.1</v>
@@ -7519,28 +7519,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M76">
-        <v>3.82791048</v>
+        <v>3.879639</v>
       </c>
       <c r="N76">
-        <v>58.63875618666667</v>
+        <v>58.58702766666667</v>
       </c>
       <c r="O76">
-        <v>17.591626856</v>
+        <v>17.5761083</v>
       </c>
       <c r="P76">
-        <v>41.04712933066666</v>
+        <v>41.01091936666667</v>
       </c>
       <c r="Q76">
-        <v>56.74712933066667</v>
+        <v>56.71091936666667</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.388832750046976</v>
+        <v>0.4011784017196178</v>
       </c>
       <c r="T76">
-        <v>2.391776144133433</v>
+        <v>2.477855491223068</v>
       </c>
       <c r="U76">
         <v>0.0503</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>16.31873759667093</v>
+        <v>16.10115442871532</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1267021004299044</v>
+        <v>0.1262522858475952</v>
       </c>
       <c r="C77">
-        <v>40.86763880490909</v>
+        <v>40.07536935343018</v>
       </c>
       <c r="D77">
-        <v>96.89763880490908</v>
+        <v>97.13376935343017</v>
       </c>
       <c r="E77">
-        <v>71.48999999999999</v>
+        <v>72.5184</v>
       </c>
       <c r="F77">
-        <v>77.13</v>
+        <v>78.1584</v>
       </c>
       <c r="G77">
         <v>21.1</v>
@@ -7601,28 +7601,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M77">
-        <v>3.879639</v>
+        <v>3.93136752</v>
       </c>
       <c r="N77">
-        <v>58.58702766666667</v>
+        <v>58.53529914666667</v>
       </c>
       <c r="O77">
-        <v>17.5761083</v>
+        <v>17.560589744</v>
       </c>
       <c r="P77">
-        <v>41.01091936666667</v>
+        <v>40.97470940266667</v>
       </c>
       <c r="Q77">
-        <v>56.71091936666667</v>
+        <v>56.67470940266666</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4011784017196178</v>
+        <v>0.4145528576983131</v>
       </c>
       <c r="T77">
-        <v>2.477855491223068</v>
+        <v>2.57110811723684</v>
       </c>
       <c r="U77">
         <v>0.0503</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>16.10115442871532</v>
+        <v>15.88929713360064</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1262522858475952</v>
+        <v>0.1258024712652858</v>
       </c>
       <c r="C78">
-        <v>40.07536935343018</v>
+        <v>39.28425356977522</v>
       </c>
       <c r="D78">
-        <v>97.13376935343017</v>
+        <v>97.37105356977523</v>
       </c>
       <c r="E78">
-        <v>72.5184</v>
+        <v>73.5468</v>
       </c>
       <c r="F78">
-        <v>78.1584</v>
+        <v>79.18680000000001</v>
       </c>
       <c r="G78">
         <v>21.1</v>
@@ -7683,28 +7683,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M78">
-        <v>3.93136752</v>
+        <v>3.98309604</v>
       </c>
       <c r="N78">
-        <v>58.53529914666667</v>
+        <v>58.48357062666667</v>
       </c>
       <c r="O78">
-        <v>17.560589744</v>
+        <v>17.545071188</v>
       </c>
       <c r="P78">
-        <v>40.97470940266667</v>
+        <v>40.93849943866667</v>
       </c>
       <c r="Q78">
-        <v>56.67470940266666</v>
+        <v>56.63849943866667</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4145528576983131</v>
+        <v>0.4290903098490688</v>
       </c>
       <c r="T78">
-        <v>2.57110811723684</v>
+        <v>2.672469667251808</v>
       </c>
       <c r="U78">
         <v>0.0503</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>15.88929713360064</v>
+        <v>15.68294262537206</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1258024712652858</v>
+        <v>0.1253526566829765</v>
       </c>
       <c r="C79">
-        <v>39.28425356977522</v>
+        <v>38.49429992939613</v>
       </c>
       <c r="D79">
-        <v>97.37105356977523</v>
+        <v>97.60949992939614</v>
       </c>
       <c r="E79">
-        <v>73.5468</v>
+        <v>74.57520000000001</v>
       </c>
       <c r="F79">
-        <v>79.18680000000001</v>
+        <v>80.21520000000001</v>
       </c>
       <c r="G79">
         <v>21.1</v>
@@ -7765,28 +7765,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M79">
-        <v>3.98309604</v>
+        <v>4.034824560000001</v>
       </c>
       <c r="N79">
-        <v>58.48357062666667</v>
+        <v>58.43184210666666</v>
       </c>
       <c r="O79">
-        <v>17.545071188</v>
+        <v>17.529552632</v>
       </c>
       <c r="P79">
-        <v>40.93849943866667</v>
+        <v>40.90228947466667</v>
       </c>
       <c r="Q79">
-        <v>56.63849943866667</v>
+        <v>56.60228947466666</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4290903098490688</v>
+        <v>0.4449493485589842</v>
       </c>
       <c r="T79">
-        <v>2.672469667251808</v>
+        <v>2.783045903631775</v>
       </c>
       <c r="U79">
         <v>0.0503</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>15.68294262537206</v>
+        <v>15.48187925838011</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1253526566829765</v>
+        <v>0.1249028421006672</v>
       </c>
       <c r="C80">
-        <v>38.49429992939613</v>
+        <v>37.70551699096869</v>
       </c>
       <c r="D80">
-        <v>97.60949992939614</v>
+        <v>97.8491169909687</v>
       </c>
       <c r="E80">
-        <v>74.57520000000001</v>
+        <v>75.6036</v>
       </c>
       <c r="F80">
-        <v>80.21520000000001</v>
+        <v>81.2436</v>
       </c>
       <c r="G80">
         <v>21.1</v>
@@ -7847,28 +7847,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M80">
-        <v>4.034824560000001</v>
+        <v>4.08655308</v>
       </c>
       <c r="N80">
-        <v>58.43184210666666</v>
+        <v>58.38011358666667</v>
       </c>
       <c r="O80">
-        <v>17.529552632</v>
+        <v>17.514034076</v>
       </c>
       <c r="P80">
-        <v>40.90228947466667</v>
+        <v>40.86607951066667</v>
       </c>
       <c r="Q80">
-        <v>56.60228947466666</v>
+        <v>56.56607951066667</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4449493485589842</v>
+        <v>0.4623187719079392</v>
       </c>
       <c r="T80">
-        <v>2.783045903631775</v>
+        <v>2.904153210143166</v>
       </c>
       <c r="U80">
         <v>0.0503</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>15.48187925838011</v>
+        <v>15.28590610321075</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1249028421006672</v>
+        <v>0.1244530275183579</v>
       </c>
       <c r="C81">
-        <v>37.70551699096869</v>
+        <v>36.9179133974168</v>
       </c>
       <c r="D81">
-        <v>97.8491169909687</v>
+        <v>98.08991339741681</v>
       </c>
       <c r="E81">
-        <v>75.6036</v>
+        <v>76.63200000000001</v>
       </c>
       <c r="F81">
-        <v>81.2436</v>
+        <v>82.27200000000001</v>
       </c>
       <c r="G81">
         <v>21.1</v>
@@ -7929,28 +7929,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M81">
-        <v>4.08655308</v>
+        <v>4.1382816</v>
       </c>
       <c r="N81">
-        <v>58.38011358666667</v>
+        <v>58.32838506666667</v>
       </c>
       <c r="O81">
-        <v>17.514034076</v>
+        <v>17.49851552</v>
       </c>
       <c r="P81">
-        <v>40.86607951066667</v>
+        <v>40.82986954666667</v>
       </c>
       <c r="Q81">
-        <v>56.56607951066667</v>
+        <v>56.52986954666667</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4623187719079392</v>
+        <v>0.4814251375917896</v>
       </c>
       <c r="T81">
-        <v>2.904153210143166</v>
+        <v>3.037371247305697</v>
       </c>
       <c r="U81">
         <v>0.0503</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>15.28590610321075</v>
+        <v>15.09483227692061</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1244530275183579</v>
+        <v>0.1240032129360486</v>
       </c>
       <c r="C82">
-        <v>36.9179133974168</v>
+        <v>36.13149787695154</v>
       </c>
       <c r="D82">
-        <v>98.08991339741681</v>
+        <v>98.33189787695156</v>
       </c>
       <c r="E82">
-        <v>76.63200000000001</v>
+        <v>77.66040000000001</v>
       </c>
       <c r="F82">
-        <v>82.27200000000001</v>
+        <v>83.30040000000001</v>
       </c>
       <c r="G82">
         <v>21.1</v>
@@ -8011,28 +8011,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M82">
-        <v>4.1382816</v>
+        <v>4.19001012</v>
       </c>
       <c r="N82">
-        <v>58.32838506666667</v>
+        <v>58.27665654666667</v>
       </c>
       <c r="O82">
-        <v>17.49851552</v>
+        <v>17.482996964</v>
       </c>
       <c r="P82">
-        <v>40.82986954666667</v>
+        <v>40.79365958266667</v>
       </c>
       <c r="Q82">
-        <v>56.52986954666667</v>
+        <v>56.49365958266667</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4814251375917896</v>
+        <v>0.5025426996634138</v>
       </c>
       <c r="T82">
-        <v>3.037371247305697</v>
+        <v>3.184612235748494</v>
       </c>
       <c r="U82">
         <v>0.0503</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>15.09483227692061</v>
+        <v>14.90847632288455</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1240032129360486</v>
+        <v>0.1235533983537393</v>
       </c>
       <c r="C83">
-        <v>36.13149787695154</v>
+        <v>35.34627924412577</v>
       </c>
       <c r="D83">
-        <v>98.33189787695156</v>
+        <v>98.57507924412577</v>
       </c>
       <c r="E83">
-        <v>77.66040000000001</v>
+        <v>78.68880000000001</v>
       </c>
       <c r="F83">
-        <v>83.30040000000001</v>
+        <v>84.32880000000002</v>
       </c>
       <c r="G83">
         <v>21.1</v>
@@ -8093,28 +8093,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M83">
-        <v>4.19001012</v>
+        <v>4.24173864</v>
       </c>
       <c r="N83">
-        <v>58.27665654666667</v>
+        <v>58.22492802666667</v>
       </c>
       <c r="O83">
-        <v>17.482996964</v>
+        <v>17.467478408</v>
       </c>
       <c r="P83">
-        <v>40.79365958266667</v>
+        <v>40.75744961866667</v>
       </c>
       <c r="Q83">
-        <v>56.49365958266667</v>
+        <v>56.45744961866667</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5025426996634138</v>
+        <v>0.526006657520774</v>
       </c>
       <c r="T83">
-        <v>3.184612235748494</v>
+        <v>3.348213334018269</v>
       </c>
       <c r="U83">
         <v>0.0503</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>14.90847632288455</v>
+        <v>14.72666563602011</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1235533983537393</v>
+        <v>0.12310358377143</v>
       </c>
       <c r="C84">
-        <v>35.34627924412577</v>
+        <v>34.56226640090446</v>
       </c>
       <c r="D84">
-        <v>98.57507924412577</v>
+        <v>98.81946640090446</v>
       </c>
       <c r="E84">
-        <v>78.68880000000001</v>
+        <v>79.71720000000001</v>
       </c>
       <c r="F84">
-        <v>84.32880000000002</v>
+        <v>85.35720000000001</v>
       </c>
       <c r="G84">
         <v>21.1</v>
@@ -8175,28 +8175,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M84">
-        <v>4.24173864</v>
+        <v>4.293467160000001</v>
       </c>
       <c r="N84">
-        <v>58.22492802666667</v>
+        <v>58.17319950666667</v>
       </c>
       <c r="O84">
-        <v>17.467478408</v>
+        <v>17.451959852</v>
       </c>
       <c r="P84">
-        <v>40.75744961866667</v>
+        <v>40.72123965466667</v>
       </c>
       <c r="Q84">
-        <v>56.45744961866667</v>
+        <v>56.42123965466666</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.526006657520774</v>
+        <v>0.5522310810084118</v>
       </c>
       <c r="T84">
-        <v>3.348213334018269</v>
+        <v>3.531061620319782</v>
       </c>
       <c r="U84">
         <v>0.0503</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>14.72666563602011</v>
+        <v>14.54923592956203</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.12310358377143</v>
+        <v>0.1226537691891207</v>
       </c>
       <c r="C85">
-        <v>34.56226640090446</v>
+        <v>33.7794683377509</v>
       </c>
       <c r="D85">
-        <v>98.81946640090446</v>
+        <v>99.0650683377509</v>
       </c>
       <c r="E85">
-        <v>79.71720000000001</v>
+        <v>80.74560000000001</v>
       </c>
       <c r="F85">
-        <v>85.35720000000001</v>
+        <v>86.38560000000001</v>
       </c>
       <c r="G85">
         <v>21.1</v>
@@ -8257,28 +8257,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M85">
-        <v>4.293467160000001</v>
+        <v>4.345195680000001</v>
       </c>
       <c r="N85">
-        <v>58.17319950666667</v>
+        <v>58.12147098666667</v>
       </c>
       <c r="O85">
-        <v>17.451959852</v>
+        <v>17.436441296</v>
       </c>
       <c r="P85">
-        <v>40.72123965466667</v>
+        <v>40.68502969066667</v>
       </c>
       <c r="Q85">
-        <v>56.42123965466666</v>
+        <v>56.38502969066667</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5522310810084118</v>
+        <v>0.5817335574320045</v>
       </c>
       <c r="T85">
-        <v>3.531061620319782</v>
+        <v>3.736765942408984</v>
       </c>
       <c r="U85">
         <v>0.0503</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>14.54923592956203</v>
+        <v>14.37603073992439</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1226537691891207</v>
+        <v>0.1222039546068114</v>
       </c>
       <c r="C86">
-        <v>33.77946833775091</v>
+        <v>32.99789413472924</v>
       </c>
       <c r="D86">
-        <v>99.0650683377509</v>
+        <v>99.31189413472923</v>
       </c>
       <c r="E86">
-        <v>80.7456</v>
+        <v>81.774</v>
       </c>
       <c r="F86">
-        <v>86.3856</v>
+        <v>87.414</v>
       </c>
       <c r="G86">
         <v>21.1</v>
@@ -8339,28 +8339,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M86">
-        <v>4.34519568</v>
+        <v>4.3969242</v>
       </c>
       <c r="N86">
-        <v>58.12147098666667</v>
+        <v>58.06974246666667</v>
       </c>
       <c r="O86">
-        <v>17.436441296</v>
+        <v>17.42092274</v>
       </c>
       <c r="P86">
-        <v>40.68502969066667</v>
+        <v>40.64881972666667</v>
       </c>
       <c r="Q86">
-        <v>56.38502969066667</v>
+        <v>56.34881972666668</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5817335574320041</v>
+        <v>0.6151696973787424</v>
       </c>
       <c r="T86">
-        <v>3.736765942408981</v>
+        <v>3.96989750744341</v>
       </c>
       <c r="U86">
         <v>0.0503</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>14.37603073992439</v>
+        <v>14.20690096651352</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1222039546068114</v>
+        <v>0.121754140024502</v>
       </c>
       <c r="C87">
-        <v>32.99789413472924</v>
+        <v>32.21755296262349</v>
       </c>
       <c r="D87">
-        <v>99.31189413472923</v>
+        <v>99.5599529626235</v>
       </c>
       <c r="E87">
-        <v>81.774</v>
+        <v>82.80240000000001</v>
       </c>
       <c r="F87">
-        <v>87.414</v>
+        <v>88.44240000000001</v>
       </c>
       <c r="G87">
         <v>21.1</v>
@@ -8421,28 +8421,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M87">
-        <v>4.3969242</v>
+        <v>4.44865272</v>
       </c>
       <c r="N87">
-        <v>58.06974246666667</v>
+        <v>58.01801394666667</v>
       </c>
       <c r="O87">
-        <v>17.42092274</v>
+        <v>17.405404184</v>
       </c>
       <c r="P87">
-        <v>40.64881972666667</v>
+        <v>40.61260976266666</v>
       </c>
       <c r="Q87">
-        <v>56.34881972666668</v>
+        <v>56.31260976266667</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6151696973787424</v>
+        <v>0.6533824287464431</v>
       </c>
       <c r="T87">
-        <v>3.96989750744341</v>
+        <v>4.236333581768471</v>
       </c>
       <c r="U87">
         <v>0.0503</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>14.20690096651352</v>
+        <v>14.04170444364708</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.121754140024502</v>
+        <v>0.1213043254421928</v>
       </c>
       <c r="C88">
-        <v>32.21755296262349</v>
+        <v>31.43845408407333</v>
       </c>
       <c r="D88">
-        <v>99.5599529626235</v>
+        <v>99.80925408407332</v>
       </c>
       <c r="E88">
-        <v>82.80240000000001</v>
+        <v>83.8308</v>
       </c>
       <c r="F88">
-        <v>88.44240000000001</v>
+        <v>89.4708</v>
       </c>
       <c r="G88">
         <v>21.1</v>
@@ -8503,28 +8503,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M88">
-        <v>4.44865272</v>
+        <v>4.500381239999999</v>
       </c>
       <c r="N88">
-        <v>58.01801394666667</v>
+        <v>57.96628542666667</v>
       </c>
       <c r="O88">
-        <v>17.405404184</v>
+        <v>17.389885628</v>
       </c>
       <c r="P88">
-        <v>40.61260976266666</v>
+        <v>40.57639979866667</v>
       </c>
       <c r="Q88">
-        <v>56.31260976266667</v>
+        <v>56.27639979866667</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6533824287464431</v>
+        <v>0.6974740418630212</v>
       </c>
       <c r="T88">
-        <v>4.236333581768471</v>
+        <v>4.543759821374311</v>
       </c>
       <c r="U88">
         <v>0.0503</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>14.04170444364708</v>
+        <v>13.88030554199597</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1213043254421928</v>
+        <v>0.1208545108598835</v>
       </c>
       <c r="C89">
-        <v>31.43845408407333</v>
+        <v>30.66060685472701</v>
       </c>
       <c r="D89">
-        <v>99.80925408407332</v>
+        <v>100.059806854727</v>
       </c>
       <c r="E89">
-        <v>83.8308</v>
+        <v>84.8592</v>
       </c>
       <c r="F89">
-        <v>89.4708</v>
+        <v>90.4992</v>
       </c>
       <c r="G89">
         <v>21.1</v>
@@ -8585,28 +8585,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M89">
-        <v>4.500381239999999</v>
+        <v>4.55210976</v>
       </c>
       <c r="N89">
-        <v>57.96628542666667</v>
+        <v>57.91455690666667</v>
       </c>
       <c r="O89">
-        <v>17.389885628</v>
+        <v>17.374367072</v>
       </c>
       <c r="P89">
-        <v>40.57639979866667</v>
+        <v>40.54018983466667</v>
       </c>
       <c r="Q89">
-        <v>56.27639979866667</v>
+        <v>56.24018983466667</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6974740418630212</v>
+        <v>0.7489142571656955</v>
       </c>
       <c r="T89">
-        <v>4.543759821374311</v>
+        <v>4.902423767581125</v>
       </c>
       <c r="U89">
         <v>0.0503</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>13.88030554199597</v>
+        <v>13.72257479720056</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1208545108598835</v>
+        <v>0.1204046962775741</v>
       </c>
       <c r="C90">
-        <v>30.66060685472701</v>
+        <v>29.88402072441178</v>
       </c>
       <c r="D90">
-        <v>100.059806854727</v>
+        <v>100.3116207244118</v>
       </c>
       <c r="E90">
-        <v>84.8592</v>
+        <v>85.88760000000001</v>
       </c>
       <c r="F90">
-        <v>90.4992</v>
+        <v>91.52760000000001</v>
       </c>
       <c r="G90">
         <v>21.1</v>
@@ -8667,28 +8667,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M90">
-        <v>4.55210976</v>
+        <v>4.60383828</v>
       </c>
       <c r="N90">
-        <v>57.91455690666667</v>
+        <v>57.86282838666667</v>
       </c>
       <c r="O90">
-        <v>17.374367072</v>
+        <v>17.358848516</v>
       </c>
       <c r="P90">
-        <v>40.54018983466667</v>
+        <v>40.50397987066667</v>
       </c>
       <c r="Q90">
-        <v>56.24018983466667</v>
+        <v>56.20397987066667</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.7489142571656955</v>
+        <v>0.8097072388870378</v>
       </c>
       <c r="T90">
-        <v>4.902423767581125</v>
+        <v>5.326299340370995</v>
       </c>
       <c r="U90">
         <v>0.0503</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>13.72257479720056</v>
+        <v>13.56838856352415</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1204046962775741</v>
+        <v>0.1199548816952648</v>
       </c>
       <c r="C91">
-        <v>29.88402072441178</v>
+        <v>29.10870523832196</v>
       </c>
       <c r="D91">
-        <v>100.3116207244118</v>
+        <v>100.564705238322</v>
       </c>
       <c r="E91">
-        <v>85.88760000000001</v>
+        <v>86.91600000000001</v>
       </c>
       <c r="F91">
-        <v>91.52760000000001</v>
+        <v>92.55600000000001</v>
       </c>
       <c r="G91">
         <v>21.1</v>
@@ -8749,28 +8749,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M91">
-        <v>4.60383828</v>
+        <v>4.655566800000001</v>
       </c>
       <c r="N91">
-        <v>57.86282838666667</v>
+        <v>57.81109986666667</v>
       </c>
       <c r="O91">
-        <v>17.358848516</v>
+        <v>17.34332996</v>
       </c>
       <c r="P91">
-        <v>40.50397987066667</v>
+        <v>40.46776990666667</v>
       </c>
       <c r="Q91">
-        <v>56.20397987066667</v>
+        <v>56.16776990666666</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.8097072388870378</v>
+        <v>0.8826588169526485</v>
       </c>
       <c r="T91">
-        <v>5.326299340370995</v>
+        <v>5.834950027718839</v>
       </c>
       <c r="U91">
         <v>0.0503</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>13.56838856352415</v>
+        <v>13.4176286905961</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1199548816952648</v>
+        <v>0.1195050671129555</v>
       </c>
       <c r="C92">
-        <v>29.10870523832196</v>
+        <v>28.33467003822484</v>
       </c>
       <c r="D92">
-        <v>100.564705238322</v>
+        <v>100.8190700382249</v>
       </c>
       <c r="E92">
-        <v>86.91600000000001</v>
+        <v>87.9444</v>
       </c>
       <c r="F92">
-        <v>92.55600000000001</v>
+        <v>93.5844</v>
       </c>
       <c r="G92">
         <v>21.1</v>
@@ -8831,28 +8831,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M92">
-        <v>4.655566800000001</v>
+        <v>4.70729532</v>
       </c>
       <c r="N92">
-        <v>57.81109986666667</v>
+        <v>57.75937134666667</v>
       </c>
       <c r="O92">
-        <v>17.34332996</v>
+        <v>17.327811404</v>
       </c>
       <c r="P92">
-        <v>40.46776990666667</v>
+        <v>40.43155994266667</v>
       </c>
       <c r="Q92">
-        <v>56.16776990666666</v>
+        <v>56.13155994266667</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.8826588169526485</v>
+        <v>0.9718218568106172</v>
       </c>
       <c r="T92">
-        <v>5.834950027718839</v>
+        <v>6.456634201143983</v>
       </c>
       <c r="U92">
         <v>0.0503</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>13.4176286905961</v>
+        <v>13.27018222146867</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1195050671129555</v>
+        <v>0.1190552525306462</v>
       </c>
       <c r="C93">
-        <v>28.33467003822484</v>
+        <v>27.56192486368532</v>
       </c>
       <c r="D93">
-        <v>100.8190700382249</v>
+        <v>101.0747248636853</v>
       </c>
       <c r="E93">
-        <v>87.9444</v>
+        <v>88.97280000000001</v>
       </c>
       <c r="F93">
-        <v>93.5844</v>
+        <v>94.61280000000001</v>
       </c>
       <c r="G93">
         <v>21.1</v>
@@ -8913,28 +8913,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M93">
-        <v>4.70729532</v>
+        <v>4.75902384</v>
       </c>
       <c r="N93">
-        <v>57.75937134666667</v>
+        <v>57.70764282666667</v>
       </c>
       <c r="O93">
-        <v>17.327811404</v>
+        <v>17.312292848</v>
       </c>
       <c r="P93">
-        <v>40.43155994266667</v>
+        <v>40.39534997866667</v>
       </c>
       <c r="Q93">
-        <v>56.13155994266667</v>
+        <v>56.09534997866668</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.9718218568106172</v>
+        <v>1.083275656633078</v>
       </c>
       <c r="T93">
-        <v>6.456634201143983</v>
+        <v>7.233739417925412</v>
       </c>
       <c r="U93">
         <v>0.0503</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>13.27018222146867</v>
+        <v>13.12594111036575</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1190552525306462</v>
+        <v>0.1186054379483369</v>
       </c>
       <c r="C94">
-        <v>27.56192486368532</v>
+        <v>26.79047955330903</v>
       </c>
       <c r="D94">
-        <v>101.0747248636853</v>
+        <v>101.331679553309</v>
       </c>
       <c r="E94">
-        <v>88.97280000000001</v>
+        <v>90.00120000000001</v>
       </c>
       <c r="F94">
-        <v>94.61280000000001</v>
+        <v>95.64120000000001</v>
       </c>
       <c r="G94">
         <v>21.1</v>
@@ -8995,28 +8995,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M94">
-        <v>4.75902384</v>
+        <v>4.81075236</v>
       </c>
       <c r="N94">
-        <v>57.70764282666667</v>
+        <v>57.65591430666667</v>
       </c>
       <c r="O94">
-        <v>17.312292848</v>
+        <v>17.296774292</v>
       </c>
       <c r="P94">
-        <v>40.39534997866667</v>
+        <v>40.35914001466666</v>
       </c>
       <c r="Q94">
-        <v>56.09534997866668</v>
+        <v>56.05914001466667</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.083275656633078</v>
+        <v>1.226573399261957</v>
       </c>
       <c r="T94">
-        <v>7.233739417925412</v>
+        <v>8.232874696644393</v>
       </c>
       <c r="U94">
         <v>0.0503</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>13.12594111036575</v>
+        <v>12.98480195864138</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1186054379483369</v>
+        <v>0.1191426233660276</v>
       </c>
       <c r="C95">
-        <v>26.79047955330903</v>
+        <v>25.45536571097915</v>
       </c>
       <c r="D95">
-        <v>101.331679553309</v>
+        <v>101.0249657109791</v>
       </c>
       <c r="E95">
-        <v>90.00120000000001</v>
+        <v>91.0296</v>
       </c>
       <c r="F95">
-        <v>95.64120000000001</v>
+        <v>96.6696</v>
       </c>
       <c r="G95">
         <v>21.1</v>
@@ -9077,45 +9077,45 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M95">
-        <v>4.81075236</v>
+        <v>5.00748528</v>
       </c>
       <c r="N95">
-        <v>57.65591430666667</v>
+        <v>57.45918138666667</v>
       </c>
       <c r="O95">
-        <v>17.296774292</v>
+        <v>17.237754416</v>
       </c>
       <c r="P95">
-        <v>40.35914001466666</v>
+        <v>40.22142697066667</v>
       </c>
       <c r="Q95">
-        <v>56.05914001466667</v>
+        <v>55.92142697066667</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.226573399261957</v>
+        <v>1.417637056100461</v>
       </c>
       <c r="T95">
-        <v>8.232874696644393</v>
+        <v>9.565055068269702</v>
       </c>
       <c r="U95">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V95">
         <v>0.3</v>
       </c>
       <c r="W95">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y95">
-        <v>12.98480195864138</v>
+        <v>12.47465807161927</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1191426233660276</v>
+        <v>0.1187033087837183</v>
       </c>
       <c r="C96">
-        <v>25.45536571097915</v>
+        <v>24.67766010495609</v>
       </c>
       <c r="D96">
-        <v>101.0249657109791</v>
+        <v>101.2756601049561</v>
       </c>
       <c r="E96">
-        <v>91.0296</v>
+        <v>92.05800000000001</v>
       </c>
       <c r="F96">
-        <v>96.6696</v>
+        <v>97.69800000000001</v>
       </c>
       <c r="G96">
         <v>21.1</v>
@@ -9159,28 +9159,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M96">
-        <v>5.00748528</v>
+        <v>5.060756400000001</v>
       </c>
       <c r="N96">
-        <v>57.45918138666667</v>
+        <v>57.40591026666667</v>
       </c>
       <c r="O96">
-        <v>17.237754416</v>
+        <v>17.22177308</v>
       </c>
       <c r="P96">
-        <v>40.22142697066667</v>
+        <v>40.18413718666667</v>
       </c>
       <c r="Q96">
-        <v>55.92142697066667</v>
+        <v>55.88413718666666</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.417637056100461</v>
+        <v>1.685126175674368</v>
       </c>
       <c r="T96">
-        <v>9.565055068269702</v>
+        <v>11.43010758854514</v>
       </c>
       <c r="U96">
         <v>0.0518</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>12.47465807161927</v>
+        <v>12.34334588139169</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1187033087837183</v>
+        <v>0.118263994201409</v>
       </c>
       <c r="C97">
-        <v>24.67766010495609</v>
+        <v>23.90120179506027</v>
       </c>
       <c r="D97">
-        <v>101.2756601049561</v>
+        <v>101.5276017950603</v>
       </c>
       <c r="E97">
-        <v>92.05800000000001</v>
+        <v>93.08640000000001</v>
       </c>
       <c r="F97">
-        <v>97.69800000000001</v>
+        <v>98.72640000000001</v>
       </c>
       <c r="G97">
         <v>21.1</v>
@@ -9241,28 +9241,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M97">
-        <v>5.060756400000001</v>
+        <v>5.11402752</v>
       </c>
       <c r="N97">
-        <v>57.40591026666667</v>
+        <v>57.35263914666667</v>
       </c>
       <c r="O97">
-        <v>17.22177308</v>
+        <v>17.205791744</v>
       </c>
       <c r="P97">
-        <v>40.18413718666667</v>
+        <v>40.14684740266667</v>
       </c>
       <c r="Q97">
-        <v>55.88413718666666</v>
+        <v>55.84684740266667</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.685126175674368</v>
+        <v>2.086359855035229</v>
       </c>
       <c r="T97">
-        <v>11.43010758854514</v>
+        <v>14.22768636895829</v>
       </c>
       <c r="U97">
         <v>0.0518</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>12.34334588139169</v>
+        <v>12.21476936179386</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.118263994201409</v>
+        <v>0.1178246796190997</v>
       </c>
       <c r="C98">
-        <v>23.90120179506032</v>
+        <v>23.12600011313678</v>
       </c>
       <c r="D98">
-        <v>101.5276017950603</v>
+        <v>101.7808001131368</v>
       </c>
       <c r="E98">
-        <v>93.0864</v>
+        <v>94.1148</v>
       </c>
       <c r="F98">
-        <v>98.7264</v>
+        <v>99.7548</v>
       </c>
       <c r="G98">
         <v>21.1</v>
@@ -9323,28 +9323,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M98">
-        <v>5.11402752</v>
+        <v>5.16729864</v>
       </c>
       <c r="N98">
-        <v>57.35263914666667</v>
+        <v>57.29936802666667</v>
       </c>
       <c r="O98">
-        <v>17.205791744</v>
+        <v>17.189810408</v>
       </c>
       <c r="P98">
-        <v>40.14684740266667</v>
+        <v>40.10955761866667</v>
       </c>
       <c r="Q98">
-        <v>55.84684740266667</v>
+        <v>55.80955761866667</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.086359855035222</v>
+        <v>2.755082653969987</v>
       </c>
       <c r="T98">
-        <v>14.22768636895825</v>
+        <v>18.89031766964682</v>
       </c>
       <c r="U98">
         <v>0.0518</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>12.21476936179387</v>
+        <v>12.08884390445579</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1178246796190997</v>
+        <v>0.1173853650367904</v>
       </c>
       <c r="C99">
-        <v>23.12600011313678</v>
+        <v>22.35206448435356</v>
       </c>
       <c r="D99">
-        <v>101.7808001131368</v>
+        <v>102.0352644843536</v>
       </c>
       <c r="E99">
-        <v>94.1148</v>
+        <v>95.14320000000001</v>
       </c>
       <c r="F99">
-        <v>99.7548</v>
+        <v>100.7832</v>
       </c>
       <c r="G99">
         <v>21.1</v>
@@ -9405,28 +9405,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M99">
-        <v>5.16729864</v>
+        <v>5.22056976</v>
       </c>
       <c r="N99">
-        <v>57.29936802666667</v>
+        <v>57.24609690666666</v>
       </c>
       <c r="O99">
-        <v>17.189810408</v>
+        <v>17.173829072</v>
       </c>
       <c r="P99">
-        <v>40.10955761866667</v>
+        <v>40.07226783466666</v>
       </c>
       <c r="Q99">
-        <v>55.80955761866667</v>
+        <v>55.77226783466666</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.755082653969987</v>
+        <v>4.092528251839515</v>
       </c>
       <c r="T99">
-        <v>18.89031766964682</v>
+        <v>28.21558027102395</v>
       </c>
       <c r="U99">
         <v>0.0518</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>12.08884390445579</v>
+        <v>11.96548835441032</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1173853650367904</v>
+        <v>0.1169460504544811</v>
       </c>
       <c r="C100">
-        <v>22.35206448435356</v>
+        <v>21.57940442837113</v>
       </c>
       <c r="D100">
-        <v>102.0352644843536</v>
+        <v>102.2910044283711</v>
       </c>
       <c r="E100">
-        <v>95.14320000000001</v>
+        <v>96.1716</v>
       </c>
       <c r="F100">
-        <v>100.7832</v>
+        <v>101.8116</v>
       </c>
       <c r="G100">
         <v>21.1</v>
@@ -9487,28 +9487,28 @@
         <v>62.46666666666667</v>
       </c>
       <c r="M100">
-        <v>5.22056976</v>
+        <v>5.27384088</v>
       </c>
       <c r="N100">
-        <v>57.24609690666666</v>
+        <v>57.19282578666667</v>
       </c>
       <c r="O100">
-        <v>17.173829072</v>
+        <v>17.157847736</v>
       </c>
       <c r="P100">
-        <v>40.07226783466666</v>
+        <v>40.03497805066667</v>
       </c>
       <c r="Q100">
-        <v>55.77226783466666</v>
+        <v>55.73497805066667</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.092528251839515</v>
+        <v>8.104865045448101</v>
       </c>
       <c r="T100">
-        <v>28.21558027102395</v>
+        <v>56.19136807515534</v>
       </c>
       <c r="U100">
         <v>0.0518</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>11.96548835441032</v>
+        <v>11.8446248356789</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1169460504544811</v>
-      </c>
-      <c r="C101">
-        <v>21.57940442837113</v>
-      </c>
-      <c r="D101">
-        <v>102.2910044283711</v>
-      </c>
-      <c r="E101">
-        <v>96.1716</v>
-      </c>
-      <c r="F101">
-        <v>101.8116</v>
-      </c>
-      <c r="G101">
-        <v>21.1</v>
-      </c>
-      <c r="H101">
-        <v>97.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>78.16666666666667</v>
-      </c>
-      <c r="K101">
-        <v>15.7</v>
-      </c>
-      <c r="L101">
-        <v>62.46666666666667</v>
-      </c>
-      <c r="M101">
-        <v>5.27384088</v>
-      </c>
-      <c r="N101">
-        <v>57.19282578666667</v>
-      </c>
-      <c r="O101">
-        <v>17.157847736</v>
-      </c>
-      <c r="P101">
-        <v>40.03497805066667</v>
-      </c>
-      <c r="Q101">
-        <v>55.73497805066667</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.104865045448101</v>
-      </c>
-      <c r="T101">
-        <v>56.19136807515534</v>
-      </c>
-      <c r="U101">
-        <v>0.0518</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.03625999999999999</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Aa2/AA</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>11.8446248356789</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
